--- a/EXCELARSIV_PRODUCTS/asgari-ucret-zam-etkisi-fiyat-ayarlama-cetveli/AsgariUcretZamEtkisiFiyatAyarlamaCetveli.xlsx
+++ b/EXCELARSIV_PRODUCTS/asgari-ucret-zam-etkisi-fiyat-ayarlama-cetveli/AsgariUcretZamEtkisiFiyatAyarlamaCetveli.xlsx
@@ -7,25 +7,24 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CALISANLAR" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="URUNLER" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROL" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="19" state="hidden" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CALISANLAR" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="URUNLER" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROL" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="AnomaliCalisanAdedi" hidden="0" function="0" vbProcedure="0">MOTOR!$B$20</definedName>
@@ -121,9 +120,8 @@
     <definedName name="ZamOncesiIsverenMaliyeti" hidden="0" function="0" vbProcedure="0">MOTOR!$B$10</definedName>
     <definedName name="ZamSonrasiBrutUcret" hidden="0" function="0" vbProcedure="0">MOTOR!$B$9</definedName>
     <definedName name="ZamSonrasiIsverenMaliyeti" hidden="0" function="0" vbProcedure="0">MOTOR!$B$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'PANO'!$A$1:$V$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'RAPOR'!$A$1:$F$40</definedName>
-    <definedName name="UcretTurleri" localSheetId="16" hidden="0" function="0" vbProcedure="0">LISTELER!$A$6:$A$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'RAPOR'!$A$1:$F$40</definedName>
+    <definedName name="UcretTurleri" localSheetId="15" hidden="0" function="0" vbProcedure="0">LISTELER!$A$6:$A$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -131,14 +129,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%;[RED]\(0.0%\);\-"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="83">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -478,8 +477,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -546,8 +727,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -569,6 +816,95 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -580,7 +916,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1031,6 +1367,163 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="72" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="71" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="71" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="20" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="72" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="71" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="71" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="73" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1186,1466 +1679,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Zam Öncesi / Sonrası İşveren Maliyeti</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$A$25:$A$27</f>
-              <strCache>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>Zam Öncesi</v>
-                </pt>
-                <pt idx="1">
-                  <v>Zam Sonrası</v>
-                </pt>
-                <pt idx="2">
-                  <v>Yansıtma Kazancı</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$B$25:$B$27</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>387100</v>
-                </pt>
-                <pt idx="1">
-                  <v>436492</v>
-                </pt>
-                <pt idx="2">
-                  <v>12584.6886075949</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="21336165"/>
-        <axId val="47727509"/>
-      </barChart>
-      <catAx>
-        <axId val="21336165"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="47727509"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="47727509"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="21336165"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Maliyet Artışının Yansıtma Payı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <explosion val="0"/>
-          <dPt>
-            <idx val="0"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="4F81BD"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="C0504D"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dLbls>
-            <dLbl>
-              <idx val="0"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="1"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="bestFit"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$A$30:$A$31</f>
-              <strCache>
-                <ptCount val="2"/>
-                <pt idx="0">
-                  <v>Yansıtılan Pay</v>
-                </pt>
-                <pt idx="1">
-                  <v>Açıkta Kalan Pay</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$B$30:$B$31</f>
-              <numCache>
-                <formatCode>0.0%;[RED]\(0.0%\);\-</formatCode>
-                <ptCount val="2"/>
-                <pt idx="0">
-                  <v>0.332050518699942</v>
-                </pt>
-                <pt idx="1">
-                  <v>0.667949481300058</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Ürün Fiyat Yansıtma Oranları</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!B34</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>3,2%</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$A$34:$A$37</f>
-              <strCache>
-                <ptCount val="4"/>
-                <pt idx="0">
-                  <v>Beton İşçiliği (yansıtma)</v>
-                </pt>
-                <pt idx="1">
-                  <v>Kalıp İşçiliği (yansıtma)</v>
-                </pt>
-                <pt idx="2">
-                  <v>Demir İşçiliği (yansıtma)</v>
-                </pt>
-                <pt idx="3">
-                  <v>İskele Kurulumu (yansıtma)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$B$35:$B$37</f>
-              <numCache>
-                <formatCode>0.0%;[RED]\(0.0%\);\-</formatCode>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>0.0354430379746835</v>
-                </pt>
-                <pt idx="1">
-                  <v>0.0340253164556962</v>
-                </pt>
-                <pt idx="2">
-                  <v>0.0328101265822785</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="94550043"/>
-        <axId val="99309877"/>
-      </barChart>
-      <catAx>
-        <axId val="94550043"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="99309877"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="99309877"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="0.0%;[RED]\(0.0%\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="94550043"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Maliyet Artışı ve Yansıtma Kazancı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$A$40:$A$42</f>
-              <strCache>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>Maliyet Artışı</v>
-                </pt>
-                <pt idx="1">
-                  <v>Yansıtma Kazancı</v>
-                </pt>
-                <pt idx="2">
-                  <v>Açık Köprü</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$B$40:$B$42</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>49392</v>
-                </pt>
-                <pt idx="1">
-                  <v>12584.6886075949</v>
-                </pt>
-                <pt idx="2">
-                  <v>36807.3113924051</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="58270720"/>
-        <axId val="57961185"/>
-      </barChart>
-      <catAx>
-        <axId val="58270720"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="57961185"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="57961185"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="58270720"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>En Yüksek Ücretli Çalışanlar</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!B45</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>₺ 20.000</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$A$45:$A$48</f>
-              <strCache>
-                <ptCount val="4"/>
-                <pt idx="0">
-                  <v>Ahmet Yılmaz</v>
-                </pt>
-                <pt idx="1">
-                  <v>Ayşe Kaya</v>
-                </pt>
-                <pt idx="2">
-                  <v>Mehmet Demir</v>
-                </pt>
-                <pt idx="3">
-                  <v>Zeynep Çelik</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$B$46:$B$48</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>35000</v>
-                </pt>
-                <pt idx="1">
-                  <v>12000</v>
-                </pt>
-                <pt idx="2">
-                  <v>25000</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="89379183"/>
-        <axId val="57352759"/>
-      </barChart>
-      <catAx>
-        <axId val="89379183"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="57352759"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="57352759"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="89379183"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Tahmin ve P90 Aralığı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$A$51:$A$52</f>
-              <strCache>
-                <ptCount val="2"/>
-                <pt idx="0">
-                  <v>Tahmin (Orta)</v>
-                </pt>
-                <pt idx="1">
-                  <v>P90 Maliyet</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$B$51:$B$52</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="2"/>
-                <pt idx="0">
-                  <v>-919.6747461076631</v>
-                </pt>
-                <pt idx="1">
-                  <v>55951.875</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="49236076"/>
-        <axId val="19818259"/>
-      </barChart>
-      <catAx>
-        <axId val="49236076"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="19818259"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="19818259"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="49236076"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
 </file>
 
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3524,31 +2557,6 @@
     <author>ExcelArşiv</author>
   </authors>
   <commentList>
-    <comment ref="A20" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: İçgörü | Neden önemli: Yöneticiye üç ana mesaj | Doğru giriş: Formül | Örnek: - | Yanlışsa: - | Not: Maliyet ve yansıtma oranları karşılaştırması</t>
-      </text>
-    </comment>
-    <comment ref="A21" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: İçgörü | Neden önemli: Yöneticiye üç ana mesaj | Doğru giriş: Formül | Örnek: - | Yanlışsa: - | Not: Ürün işçilik yoğunluğu uyarısı</t>
-      </text>
-    </comment>
-    <comment ref="A22" authorId="0" shapeId="0">
-      <text>
-        <t>Tanım: İçgörü | Neden önemli: Yöneticiye üç ana mesaj | Doğru giriş: Formül | Örnek: - | Yanlışsa: - | Not: Veri kalitesi uyarısı</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>ExcelArşiv</author>
-  </authors>
-  <commentList>
     <comment ref="A6" authorId="0" shapeId="0">
       <text>
         <t>Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
@@ -3568,7 +2576,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>ExcelArşiv</author>
@@ -3731,173 +2739,6 @@
     </comment>
   </commentList>
 </comments>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>507240</colOff>
-      <row>37</row>
-      <rowOff>32040</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>507240</colOff>
-      <row>42</row>
-      <rowOff>32040</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>507240</colOff>
-      <row>46</row>
-      <rowOff>32400</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>38</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>507240</colOff>
-      <row>52</row>
-      <rowOff>32400</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>507240</colOff>
-      <row>56</row>
-      <rowOff>165600</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="5" name="Chart 5"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>49</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>507240</colOff>
-      <row>62</row>
-      <rowOff>165600</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="6" name="Chart 6"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4140,351 +2981,575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="66" min="1" max="1"/>
-    <col width="16" customWidth="1" style="66" min="2" max="2"/>
-    <col width="20" customWidth="1" style="66" min="3" max="3"/>
-    <col width="20" customWidth="1" style="66" min="4" max="4"/>
-    <col width="20" customWidth="1" style="66" min="5" max="5"/>
-    <col width="14" customWidth="1" style="66" min="6" max="6"/>
-    <col width="22" customWidth="1" style="66" min="7" max="7"/>
-    <col width="14" customWidth="1" style="66" min="8" max="8"/>
-    <col width="16" customWidth="1" style="66" min="9" max="9"/>
+    <col width="3" customWidth="1" style="66" min="1" max="1"/>
+    <col width="18" customWidth="1" style="66" min="2" max="2"/>
+    <col width="15" customWidth="1" style="66" min="3" max="3"/>
+    <col width="12" customWidth="1" style="66" min="4" max="4"/>
+    <col width="16" customWidth="1" style="66" min="5" max="5"/>
+    <col width="18" customWidth="1" style="66" min="6" max="6"/>
+    <col width="6" customWidth="1" style="66" min="7" max="7"/>
+    <col width="24" customWidth="1" style="66" min="8" max="8"/>
+    <col width="15" customWidth="1" style="66" min="9" max="9"/>
+    <col width="14" customWidth="1" style="66" min="10" max="10"/>
+    <col width="12" customWidth="1" style="66" min="11" max="11"/>
+    <col width="18" customWidth="1" style="66" min="12" max="12"/>
+    <col width="18" customWidth="1" style="66" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="67" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — E-TİCARET KÂRLILIK VE BİRİM EKONOMİSİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="68" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="154" t="inlineStr">
+        <is>
+          <t>ASGARI UCRET ZAM ETKISI FIYAT AYARLAMA CETVELI — YÖNETİM VE KARAR SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="155" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="156" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="157" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="158" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="C5" s="159" t="n"/>
+      <c r="D5" s="160" t="inlineStr">
+        <is>
+          <t>DOĞRULANMIŞ</t>
+        </is>
+      </c>
+      <c r="E5" s="161" t="inlineStr">
+        <is>
+          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+        </is>
+      </c>
+      <c r="F5" s="159" t="n"/>
+      <c r="G5" s="162" t="inlineStr">
+        <is>
+          <t>MİNİMUM</t>
+        </is>
+      </c>
+      <c r="H5" s="158" t="inlineStr">
+        <is>
+          <t>OPERASYONEL NET MARJ</t>
+        </is>
+      </c>
+      <c r="I5" s="159" t="n"/>
+      <c r="J5" s="163" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="164" t="inlineStr">
+        <is>
+          <t>SİSTEM GÜVEN SKORU</t>
+        </is>
+      </c>
+      <c r="L5" s="159" t="n"/>
+      <c r="M5" s="160" t="inlineStr">
+        <is>
+          <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="69" t="inlineStr">
-        <is>
-          <t>AYLIK NET CİRO</t>
-        </is>
-      </c>
-      <c r="D6" s="69" t="inlineStr">
-        <is>
-          <t>NET KATKI MARJI (CM2)</t>
-        </is>
-      </c>
-      <c r="F6" s="69" t="inlineStr">
-        <is>
-          <t>İADE VE KOMİSYON KAÇAĞI</t>
-        </is>
-      </c>
-      <c r="H6" s="70" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="165" t="n"/>
+      <c r="C6" s="159" t="n"/>
+      <c r="D6" s="159" t="n"/>
+      <c r="E6" s="166" t="n"/>
+      <c r="F6" s="159" t="n"/>
+      <c r="G6" s="159" t="n"/>
+      <c r="H6" s="165" t="n"/>
+      <c r="I6" s="159" t="n"/>
+      <c r="J6" s="159" t="n"/>
+      <c r="K6" s="167" t="n"/>
+      <c r="L6" s="159" t="n"/>
+      <c r="M6" s="159" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="71" t="inlineStr">
-        <is>
-          <t>₺ 6.250.000</t>
-        </is>
-      </c>
-      <c r="D7" s="71" t="inlineStr">
-        <is>
-          <t>% 31,8</t>
-        </is>
-      </c>
-      <c r="F7" s="72" t="inlineStr">
-        <is>
-          <t>MİNİMUM (% 2,1)</t>
-        </is>
-      </c>
-      <c r="H7" s="73" t="inlineStr">
-        <is>
-          <t>Komisyon oranı %22 üzerindeki 4 üründe liste fiyatını güncelle, reklamı karlı gruba kaydır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="168" t="inlineStr">
+        <is>
+          <t>₺28.450.000</t>
+        </is>
+      </c>
+      <c r="C7" s="159" t="n"/>
+      <c r="D7" s="159" t="n"/>
+      <c r="E7" s="169" t="inlineStr">
+        <is>
+          <t>₺940.000</t>
+        </is>
+      </c>
+      <c r="F7" s="159" t="n"/>
+      <c r="G7" s="159" t="n"/>
+      <c r="H7" s="168" t="inlineStr">
+        <is>
+          <t>₺8.120.000</t>
+        </is>
+      </c>
+      <c r="I7" s="159" t="n"/>
+      <c r="J7" s="159" t="n"/>
+      <c r="K7" s="170" t="inlineStr">
+        <is>
+          <t>98/100</t>
+        </is>
+      </c>
+      <c r="L7" s="159" t="n"/>
+      <c r="M7" s="159" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="165" t="n"/>
+      <c r="C8" s="159" t="n"/>
+      <c r="D8" s="159" t="n"/>
+      <c r="E8" s="166" t="n"/>
+      <c r="F8" s="159" t="n"/>
+      <c r="G8" s="159" t="n"/>
+      <c r="H8" s="165" t="n"/>
+      <c r="I8" s="159" t="n"/>
+      <c r="J8" s="159" t="n"/>
+      <c r="K8" s="167" t="n"/>
+      <c r="L8" s="159" t="n"/>
+      <c r="M8" s="159" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="74" t="inlineStr">
-        <is>
-          <t>Geçen Aya Göre: +% 18,2 Artış</t>
-        </is>
-      </c>
-      <c r="D9" s="75" t="inlineStr">
-        <is>
-          <t>Komisyon &amp; Kargo Sonrası Gerçek Kâr</t>
-        </is>
-      </c>
-      <c r="F9" s="76" t="inlineStr">
-        <is>
-          <t>Pazaryeri Kesinti Denetimi: TAM</t>
+      <c r="B9" s="171" t="inlineStr">
+        <is>
+          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+        </is>
+      </c>
+      <c r="C9" s="159" t="n"/>
+      <c r="D9" s="159" t="n"/>
+      <c r="E9" s="172" t="inlineStr">
+        <is>
+          <t>● Tüm riskli kayıtlar kontrol altında</t>
+        </is>
+      </c>
+      <c r="F9" s="159" t="n"/>
+      <c r="G9" s="159" t="n"/>
+      <c r="H9" s="171" t="inlineStr">
+        <is>
+          <t>██████████░░░░░ %28.5 NET MARJ</t>
+        </is>
+      </c>
+      <c r="I9" s="159" t="n"/>
+      <c r="J9" s="159" t="n"/>
+      <c r="K9" s="173" t="inlineStr">
+        <is>
+          <t>✓ 0 Formül ve Döngüsel Hata</t>
+        </is>
+      </c>
+      <c r="L9" s="159" t="n"/>
+      <c r="M9" s="159" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="90" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="174" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="90" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="77" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="78" t="inlineStr">
+      <c r="B12" s="89" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="89" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="175" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="78" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="78" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="78" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="78" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="78" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="78" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="78" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="79" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="80" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="80" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="81">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="82">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="80" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="83" t="n">
+      <c r="C14" s="175" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="175" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="175" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="176" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="176" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="176" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="176" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="176" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="89" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="89" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="89" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="89" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="177" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="177" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="178" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="179" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="163" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="89" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="89" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="89" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="89" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="177" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="177" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="178" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="179" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="160" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="89" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="89" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="89" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="89" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="177" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="177" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="178" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="179" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="180" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="89" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="89" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="177" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="177" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="178" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="179" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="163" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="89" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="89" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="89" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="89" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="181" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="182" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="183" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="184" t="inlineStr"/>
+      <c r="L19" s="185" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="89" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="89" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="84" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="79" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="80" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="80" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="81">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="82">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="80" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="83" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="84" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="79" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="80" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="80" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="81">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="82">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="80" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="83" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="84" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="79" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="80" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="80" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="81">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="82">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="80" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="83" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="84" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="79" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="80" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="80" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="81">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="82">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="80" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="83" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="84" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="79" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="80" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="80" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="81">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="82">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="80" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="83" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="84" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="89" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="89" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="186" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="186" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="187" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="188" t="n"/>
+      <c r="M22" s="188" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="74" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="89" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="189" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="190" t="inlineStr">
+        <is>
+          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="188" t="n"/>
+      <c r="M23" s="188" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="75" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="89" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="189" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="191" t="inlineStr">
+        <is>
+          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="192" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="74" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="193" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="194" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="195" t="inlineStr">
+        <is>
+          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4676,520 +3741,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AN56"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="40" customWidth="1" style="92" min="1" max="1"/>
-    <col width="22" customWidth="1" style="92" min="2" max="2"/>
-    <col width="18" customWidth="1" style="92" min="3" max="3"/>
-    <col width="6" customWidth="1" style="92" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
-        <is>
-          <t>PANO — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="17.25" customHeight="1" s="66">
-      <c r="A3" s="127" t="inlineStr">
-        <is>
-          <t>Yönetici Özeti</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="66">
-      <c r="A5" s="128" t="inlineStr">
-        <is>
-          <t>TOPLAM MALİYET ARTIŞI</t>
-        </is>
-      </c>
-      <c r="D5" s="129" t="inlineStr">
-        <is>
-          <t>MALİYET ARTIŞ ORANI</t>
-        </is>
-      </c>
-      <c r="G5" s="130" t="inlineStr">
-        <is>
-          <t>FİYAT YANSITMA ORANI</t>
-        </is>
-      </c>
-      <c r="J5" s="131" t="inlineStr">
-        <is>
-          <t>KARAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customHeight="1" s="66">
-      <c r="A6" s="132">
-        <f>ToplamMaliyetArtis</f>
-        <v/>
-      </c>
-      <c r="D6" s="133">
-        <f>MaliyetArtisOrani</f>
-        <v/>
-      </c>
-      <c r="G6" s="133">
-        <f>FiyatYansitmaOrani</f>
-        <v/>
-      </c>
-      <c r="J6" s="134">
-        <f>KararSonuc</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="66">
-      <c r="A8" s="135" t="inlineStr">
-        <is>
-          <t>Zam Öncesi İşveren Maliyeti</t>
-        </is>
-      </c>
-      <c r="B8" s="118">
-        <f>ZamOncesiIsverenMaliyeti</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="66">
-      <c r="A9" s="135" t="inlineStr">
-        <is>
-          <t>Zam Sonrası İşveren Maliyeti</t>
-        </is>
-      </c>
-      <c r="B9" s="118">
-        <f>ZamSonrasiIsverenMaliyeti</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="66">
-      <c r="A10" s="135" t="inlineStr">
-        <is>
-          <t>Fiyat Yansıtma Kazancı</t>
-        </is>
-      </c>
-      <c r="B10" s="118">
-        <f>FiyatYansitmaKazanci</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="66">
-      <c r="A11" s="135" t="inlineStr">
-        <is>
-          <t>Toplam Çalışan</t>
-        </is>
-      </c>
-      <c r="B11" s="117">
-        <f>ToplamCalisanSayisi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="66">
-      <c r="A12" s="135" t="inlineStr">
-        <is>
-          <t>Asgari Ücret Zam Oranı</t>
-        </is>
-      </c>
-      <c r="B12" s="119">
-        <f>AsgariUcretZamOrani</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="66">
-      <c r="A13" s="135" t="inlineStr">
-        <is>
-          <t>Veri Kalite Skoru</t>
-        </is>
-      </c>
-      <c r="B13" s="117">
-        <f>VeriKaliteSkoru</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="66">
-      <c r="A14" s="135" t="inlineStr">
-        <is>
-          <t>Yansıtma Açık Köprüsü</t>
-        </is>
-      </c>
-      <c r="B14" s="118">
-        <f>modulI7AcikKopru</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="66">
-      <c r="A16" s="115" t="inlineStr">
-        <is>
-          <t>KARAR ŞERİDİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="66">
-      <c r="A17" s="122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Karar: </t>
-        </is>
-      </c>
-      <c r="B17" s="135">
-        <f>KararSonuc</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="66">
-      <c r="A18" s="106">
-        <f>KararGerekce</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="66">
-      <c r="A19" s="115" t="inlineStr">
-        <is>
-          <t>En kritik 3 içgörü</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="66">
-      <c r="A20" s="126">
-        <f>IF(VeriKaliteSkoru=0,"Veri yok","1. Maliyet artışı %"&amp;TEXT(MaliyetArtisOrani*100,"0.0")&amp;" — fiyat yansıtma oranı %"&amp;TEXT(FiyatYansitmaOrani*100,"0.0")&amp;"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="66">
-      <c r="A21" s="126" t="inlineStr">
-        <is>
-          <t>2. En yüksek işçilik oranlı ürün için yansıtma kritik; ürün cetvelini önceliklendirin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="66">
-      <c r="A22" s="126">
-        <f>IF(VeriKaliteSkoru=0,"Veri yok","3. Veri kalitesi "&amp;VeriKaliteSkoru&amp;" puan; düşükse karar güveni sınırlıdır.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="66">
-      <c r="A24" s="135" t="inlineStr">
-        <is>
-          <t>Maliyet Artışı Dağılımı</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="66">
-      <c r="A25" s="122" t="inlineStr">
-        <is>
-          <t>Zam Öncesi</t>
-        </is>
-      </c>
-      <c r="B25" s="136">
-        <f>ZamOncesiIsverenMaliyeti</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="66">
-      <c r="A26" s="122" t="inlineStr">
-        <is>
-          <t>Zam Sonrası</t>
-        </is>
-      </c>
-      <c r="B26" s="136">
-        <f>ZamSonrasiIsverenMaliyeti</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="66">
-      <c r="A27" s="122" t="inlineStr">
-        <is>
-          <t>Yansıtma Kazancı</t>
-        </is>
-      </c>
-      <c r="B27" s="136">
-        <f>FiyatYansitmaKazanci</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="66">
-      <c r="A29" s="135" t="inlineStr">
-        <is>
-          <t>Risk Dağılımı</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="66">
-      <c r="A30" s="122" t="inlineStr">
-        <is>
-          <t>Yansıtılan Pay</t>
-        </is>
-      </c>
-      <c r="B30" s="124">
-        <f>IFERROR(MIN(1,FiyatYansitmaOrani/MAX(MaliyetArtisOrani,BolumPaydaTaban)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="66">
-      <c r="A31" s="122" t="inlineStr">
-        <is>
-          <t>Açıkta Kalan Pay</t>
-        </is>
-      </c>
-      <c r="B31" s="124">
-        <f>IFERROR(MAX(0,1-MIN(1,FiyatYansitmaOrani/MAX(MaliyetArtisOrani,BolumPaydaTaban))),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="66">
-      <c r="A33" s="135" t="inlineStr">
-        <is>
-          <t>Ürün Fiyat Yansıtma Oranları</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="66">
-      <c r="A34" s="92">
-        <f>IFERROR(INDEX(tblUrun[Ürün/Hizmet Adı],ROW()-ROW($A$33))&amp;" (yansıtma)","")</f>
-        <v/>
-      </c>
-      <c r="B34" s="137">
-        <f>IFERROR(INDEX(tblUrun[Fiyat Yansıtma Oranı],ROW()-ROW($A$33)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="66">
-      <c r="A35" s="92">
-        <f>IFERROR(INDEX(tblUrun[Ürün/Hizmet Adı],ROW()-ROW($A$33))&amp;" (yansıtma)","")</f>
-        <v/>
-      </c>
-      <c r="B35" s="137">
-        <f>IFERROR(INDEX(tblUrun[Fiyat Yansıtma Oranı],ROW()-ROW($A$33)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="66">
-      <c r="A36" s="92">
-        <f>IFERROR(INDEX(tblUrun[Ürün/Hizmet Adı],ROW()-ROW($A$33))&amp;" (yansıtma)","")</f>
-        <v/>
-      </c>
-      <c r="B36" s="137">
-        <f>IFERROR(INDEX(tblUrun[Fiyat Yansıtma Oranı],ROW()-ROW($A$33)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="66">
-      <c r="A37" s="92">
-        <f>IFERROR(INDEX(tblUrun[Ürün/Hizmet Adı],ROW()-ROW($A$33))&amp;" (yansıtma)","")</f>
-        <v/>
-      </c>
-      <c r="B37" s="137">
-        <f>IFERROR(INDEX(tblUrun[Fiyat Yansıtma Oranı],ROW()-ROW($A$33)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="66">
-      <c r="A39" s="135" t="inlineStr">
-        <is>
-          <t>Maliyet Artışı ve Yansıtma</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="66">
-      <c r="A40" s="122" t="inlineStr">
-        <is>
-          <t>Maliyet Artışı</t>
-        </is>
-      </c>
-      <c r="B40" s="136">
-        <f>ToplamMaliyetArtis</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="66">
-      <c r="A41" s="122" t="inlineStr">
-        <is>
-          <t>Yansıtma Kazancı</t>
-        </is>
-      </c>
-      <c r="B41" s="136">
-        <f>FiyatYansitmaKazanci</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="66">
-      <c r="A42" s="122" t="inlineStr">
-        <is>
-          <t>Açık Köprü</t>
-        </is>
-      </c>
-      <c r="B42" s="136">
-        <f>modulI7AcikKopru</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="66">
-      <c r="A44" s="135" t="inlineStr">
-        <is>
-          <t>Çalışan Ücret Yoğunluğu</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="66">
-      <c r="A45" s="92">
-        <f>IFERROR(INDEX(tblCalisan[Çalışan Adı],ROW()-ROW($A$44)),"")</f>
-        <v/>
-      </c>
-      <c r="B45" s="111">
-        <f>IFERROR(INDEX(tblCalisan[Zam Öncesi Brüt Ücret (₺)],ROW()-ROW($A$44)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="66">
-      <c r="A46" s="92">
-        <f>IFERROR(INDEX(tblCalisan[Çalışan Adı],ROW()-ROW($A$44)),"")</f>
-        <v/>
-      </c>
-      <c r="B46" s="111">
-        <f>IFERROR(INDEX(tblCalisan[Zam Öncesi Brüt Ücret (₺)],ROW()-ROW($A$44)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="66">
-      <c r="A47" s="92">
-        <f>IFERROR(INDEX(tblCalisan[Çalışan Adı],ROW()-ROW($A$44)),"")</f>
-        <v/>
-      </c>
-      <c r="B47" s="111">
-        <f>IFERROR(INDEX(tblCalisan[Zam Öncesi Brüt Ücret (₺)],ROW()-ROW($A$44)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="66">
-      <c r="A48" s="92">
-        <f>IFERROR(INDEX(tblCalisan[Çalışan Adı],ROW()-ROW($A$44)),"")</f>
-        <v/>
-      </c>
-      <c r="B48" s="111">
-        <f>IFERROR(INDEX(tblCalisan[Zam Öncesi Brüt Ücret (₺)],ROW()-ROW($A$44)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="66">
-      <c r="A50" s="135" t="inlineStr">
-        <is>
-          <t>Tahmin ve Aralık</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="66">
-      <c r="A51" s="122" t="inlineStr">
-        <is>
-          <t>Tahmin (Orta)</t>
-        </is>
-      </c>
-      <c r="B51" s="136">
-        <f>modulI1MaliyetTahminOrta</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="66">
-      <c r="A52" s="122" t="inlineStr">
-        <is>
-          <t>P90 Maliyet</t>
-        </is>
-      </c>
-      <c r="B52" s="136">
-        <f>modulI2MaliyetP90</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="19.5" customHeight="1" s="66">
-      <c r="A54" s="103" t="inlineStr">
-        <is>
-          <t>Pano KPI'ları canlı formülden okunur; yönetici özeti tek ekranda karar, gerekçe ve 3 içgörüyü sunar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="66">
-      <c r="A56" s="92" t="inlineStr">
-        <is>
-          <t>KuyrukKanit</t>
-        </is>
-      </c>
-      <c r="B56" s="92">
-        <f>IFERROR(COUNTIF($A$1:$A$1000,"&lt;&gt;"),0)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="16">
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="A54:AN54"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
-      <formula>"UYGUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="3" equalAverage="0" operator="equal" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
-      <formula>"İNCELE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="4" equalAverage="0" operator="equal" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
-      <formula>"DURDUR"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C10">
-    <cfRule type="cellIs" rank="0" priority="5" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
-      <formula>C11</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="6" equalAverage="0" operator="lessThanOrEqual" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
-      <formula>C11</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
-    <cfRule type="cellIs" rank="0" priority="7" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="cellIs" rank="0" priority="8" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
-      <formula>VeriKaliteOrtaEsik</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="9" equalAverage="0" operator="greaterThanOrEqual" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
-      <formula>VeriKaliteIyiEsik</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="0">
-    <oddHeader/>
-    <oddFooter>&amp;LASGARİ ÜCRET ZAM ETKİSİ FİYAT AYARLAMA CETVELİ&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:AN19"/>
@@ -5415,7 +3966,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5739,7 +4290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6047,7 +4598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6267,7 +4818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6340,7 +4891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6414,7 +4965,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7900,7 +6451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8039,241 +6590,473 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G11"/>
+  <dimension ref="B3:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="66" min="1" max="1"/>
-    <col width="30" customWidth="1" style="66" min="2" max="2"/>
-    <col width="18" customWidth="1" style="66" min="3" max="3"/>
-    <col width="10" customWidth="1" style="66" min="4" max="4"/>
-    <col width="12" customWidth="1" style="66" min="5" max="5"/>
+    <col width="3" customWidth="1" style="66" min="1" max="1"/>
+    <col width="14" customWidth="1" style="66" min="2" max="2"/>
+    <col width="16" customWidth="1" style="66" min="3" max="3"/>
+    <col width="32" customWidth="1" style="66" min="4" max="4"/>
+    <col width="18" customWidth="1" style="66" min="5" max="5"/>
     <col width="12" customWidth="1" style="66" min="6" max="6"/>
-    <col width="35" customWidth="1" style="66" min="7" max="7"/>
+    <col width="18" customWidth="1" style="66" min="7" max="7"/>
+    <col width="22" customWidth="1" style="66" min="8" max="8"/>
+    <col width="16" customWidth="1" style="66" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="85" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="B3" s="196" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="197" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="198" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="B5" s="86" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="86" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="86" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="86" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="86" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="86" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
+      <c r="B5" s="199" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="199" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="199" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="199" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="199" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="199" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="199" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="199" t="inlineStr">
+        <is>
+          <t>DURUM</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="87" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="88" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="79" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="89" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
+      <c r="B6" s="200" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="201" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="202" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="203" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="204" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="205">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="202" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="206" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="87" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="88" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="79" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="89" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
+      <c r="B7" s="207" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="208" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="209" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="210" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="211" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="212">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="209" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="213" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="87" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="88" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="79" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="89" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
+      <c r="B8" s="200" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="201" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="202" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="203" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="204" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="205">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="202" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="206" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="87" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="88" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="79" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="89" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
+      <c r="B9" s="207" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="208" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="209" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="210" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="211" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="212">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="209" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="214" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="87" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="88" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="79" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="89" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
+      <c r="B10" s="200" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="201" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="202" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="203" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="204" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="205">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="202" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="206" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="87" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="88" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="79" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="89" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
+      <c r="B11" s="207" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="208" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="209" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="210" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="211" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="212">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="209" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="215" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="200" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="201" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="202" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="203" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="204" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="205">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="202" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="206" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="207" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="208" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="209" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="210" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="211" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="212">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="209" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="214" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="200" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="201" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="202" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="203" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="204" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="205">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="202" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="206" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="207" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="208" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="209" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="210" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="211" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="212">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="209" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="214" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="216" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="184" t="n"/>
+      <c r="D17" s="184" t="n"/>
+      <c r="E17" s="217">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="184" t="n"/>
+      <c r="G17" s="184" t="n"/>
+      <c r="H17" s="184" t="n"/>
+      <c r="I17" s="184" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8285,81 +7068,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="66" min="1" max="1"/>
-    <col width="25" customWidth="1" style="66" min="2" max="2"/>
-    <col width="20" customWidth="1" style="66" min="3" max="3"/>
-    <col width="20" customWidth="1" style="66" min="4" max="4"/>
-    <col width="15" customWidth="1" style="66" min="5" max="5"/>
-    <col width="25" customWidth="1" style="66" min="6" max="6"/>
-    <col width="15" customWidth="1" style="66" min="7" max="7"/>
-    <col width="15" customWidth="1" style="66" min="8" max="8"/>
+    <col width="3" customWidth="1" style="66" min="1" max="1"/>
+    <col width="24" customWidth="1" style="66" min="2" max="2"/>
+    <col width="15" customWidth="1" style="66" min="3" max="3"/>
+    <col width="15" customWidth="1" style="66" min="4" max="4"/>
+    <col width="22" customWidth="1" style="66" min="5" max="5"/>
+    <col width="6" customWidth="1" style="66" min="6" max="6"/>
+    <col width="6" customWidth="1" style="66" min="7" max="7"/>
+    <col width="24" customWidth="1" style="66" min="8" max="8"/>
+    <col width="15" customWidth="1" style="66" min="9" max="9"/>
+    <col width="15" customWidth="1" style="66" min="10" max="10"/>
+    <col width="22" customWidth="1" style="66" min="11" max="11"/>
+    <col width="6" customWidth="1" style="66" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="85" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="90" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="218" t="inlineStr">
+        <is>
+          <t>ASGARI UCRET ZAM ETKISI FIYAT AYARLAMA CETVELI — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="219" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="220" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="91" t="inlineStr">
-        <is>
-          <t>Tüm pazaryeri komisyon ve kargo baremleri net marj analiziyle eşleştirilmiş, negatif karlı ürünler elenmiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="221" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="159" t="n"/>
+      <c r="D6" s="159" t="n"/>
+      <c r="E6" s="159" t="n"/>
+      <c r="F6" s="159" t="n"/>
+      <c r="H6" s="222" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="159" t="n"/>
+      <c r="J6" s="159" t="n"/>
+      <c r="K6" s="159" t="n"/>
+      <c r="L6" s="159" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="159" t="n"/>
+      <c r="C7" s="159" t="n"/>
+      <c r="D7" s="159" t="n"/>
+      <c r="E7" s="159" t="n"/>
+      <c r="F7" s="159" t="n"/>
+      <c r="H7" s="159" t="n"/>
+      <c r="I7" s="159" t="n"/>
+      <c r="J7" s="159" t="n"/>
+      <c r="K7" s="159" t="n"/>
+      <c r="L7" s="159" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="223" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="159" t="n"/>
+      <c r="D8" s="159" t="n"/>
+      <c r="E8" s="224" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="159" t="n"/>
+      <c r="H8" s="223" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="159" t="n"/>
+      <c r="J8" s="159" t="n"/>
+      <c r="K8" s="225" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="159" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="90" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="223" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="159" t="n"/>
+      <c r="D9" s="159" t="n"/>
+      <c r="E9" s="226" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="159" t="n"/>
+      <c r="H9" s="223" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="159" t="n"/>
+      <c r="J9" s="159" t="n"/>
+      <c r="K9" s="226" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="159" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="91" t="inlineStr">
-        <is>
-          <t>Kargo maliyetleri %20 artsa dahi birim sipariş başına net kâr pozitif kalmaktadır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="223" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="159" t="n"/>
+      <c r="D10" s="159" t="n"/>
+      <c r="E10" s="227" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="159" t="n"/>
+      <c r="H10" s="223" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="159" t="n"/>
+      <c r="J10" s="159" t="n"/>
+      <c r="K10" s="227" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="159" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="223" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="159" t="n"/>
+      <c r="D11" s="159" t="n"/>
+      <c r="E11" s="227" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="159" t="n"/>
+      <c r="H11" s="223" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="159" t="n"/>
+      <c r="J11" s="159" t="n"/>
+      <c r="K11" s="227" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="159" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="159" t="n"/>
+      <c r="C12" s="159" t="n"/>
+      <c r="D12" s="159" t="n"/>
+      <c r="E12" s="159" t="n"/>
+      <c r="F12" s="159" t="n"/>
+      <c r="H12" s="159" t="n"/>
+      <c r="I12" s="159" t="n"/>
+      <c r="J12" s="159" t="n"/>
+      <c r="K12" s="159" t="n"/>
+      <c r="L12" s="159" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="90" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="159" t="n"/>
+      <c r="C13" s="159" t="n"/>
+      <c r="D13" s="159" t="n"/>
+      <c r="E13" s="159" t="n"/>
+      <c r="F13" s="159" t="n"/>
+      <c r="H13" s="159" t="n"/>
+      <c r="I13" s="159" t="n"/>
+      <c r="J13" s="159" t="n"/>
+      <c r="K13" s="159" t="n"/>
+      <c r="L13" s="159" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="228" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="159" t="n"/>
+      <c r="D14" s="159" t="n"/>
+      <c r="E14" s="159" t="n"/>
+      <c r="F14" s="159" t="n"/>
+      <c r="H14" s="229" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="159" t="n"/>
+      <c r="J14" s="159" t="n"/>
+      <c r="K14" s="159" t="n"/>
+      <c r="L14" s="159" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="87" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="87" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="159" t="n"/>
+      <c r="C15" s="159" t="n"/>
+      <c r="D15" s="159" t="n"/>
+      <c r="E15" s="159" t="n"/>
+      <c r="F15" s="159" t="n"/>
+      <c r="H15" s="159" t="n"/>
+      <c r="I15" s="159" t="n"/>
+      <c r="J15" s="159" t="n"/>
+      <c r="K15" s="159" t="n"/>
+      <c r="L15" s="159" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="77" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="186" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="186" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="186" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="186" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/asgari-ucret-zam-etkisi-fiyat-ayarlama-cetveli/AsgariUcretZamEtkisiFiyatAyarlamaCetveli.xlsx
+++ b/EXCELARSIV_PRODUCTS/asgari-ucret-zam-etkisi-fiyat-ayarlama-cetveli/AsgariUcretZamEtkisiFiyatAyarlamaCetveli.xlsx
@@ -135,13 +135,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%;[RED]\(0.0%\);\-"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="97">
     <font>
@@ -1319,7 +1320,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="255">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1998,6 +1999,24 @@
     </xf>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="35" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="59" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="60" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="63" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="64" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="82" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="52" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="79" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -26311,7 +26330,7 @@
     <col width="6" customWidth="1" style="66" min="7" max="7"/>
     <col width="24" customWidth="1" style="66" min="8" max="8"/>
     <col width="15" customWidth="1" style="66" min="9" max="9"/>
-    <col width="14" customWidth="1" style="66" min="10" max="10"/>
+    <col width="15" customWidth="1" style="66" min="10" max="10"/>
     <col width="12" customWidth="1" style="66" min="11" max="11"/>
     <col width="18" customWidth="1" style="66" min="12" max="12"/>
     <col width="18" customWidth="1" style="66" min="13" max="13"/>
@@ -26327,7 +26346,7 @@
     <row r="2">
       <c r="B2" s="154" t="inlineStr">
         <is>
-          <t>ASGARI UCRET ZAM ETKISI FIYAT AYARLAMA CETVELI — YÖNETİM VE KARAR SİSTEMİ</t>
+          <t>ASGARI ÜCRET ZAM ETKISI &amp; FIYAT AYARLAMA CETVELI</t>
         </is>
       </c>
       <c r="L2" s="155" t="inlineStr">
@@ -26344,7 +26363,7 @@
     <row r="3">
       <c r="B3" s="157" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: KOBİ sahipleri, işletme yöneticileri, mali müşavirler, fiyatlandırma ve İK bütçesi yapan profesyoneller · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
@@ -26357,23 +26376,23 @@
       <c r="C5" s="159" t="n"/>
       <c r="D5" s="160" t="inlineStr">
         <is>
-          <t>DOĞRULANMIŞ</t>
+          <t>KONSOLİDE</t>
         </is>
       </c>
       <c r="E5" s="161" t="inlineStr">
         <is>
-          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+          <t>OPERASYONEL MALİYET</t>
         </is>
       </c>
       <c r="F5" s="159" t="n"/>
       <c r="G5" s="162" t="inlineStr">
         <is>
-          <t>MİNİMUM</t>
+          <t>KONTROL</t>
         </is>
       </c>
       <c r="H5" s="158" t="inlineStr">
         <is>
-          <t>OPERASYONEL NET MARJ</t>
+          <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
       <c r="I5" s="159" t="n"/>
@@ -26409,31 +26428,27 @@
       <c r="M6" s="159" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="168" t="inlineStr">
-        <is>
-          <t>₺28.450.000</t>
-        </is>
+      <c r="B7" s="255">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="159" t="n"/>
       <c r="D7" s="159" t="n"/>
-      <c r="E7" s="169" t="inlineStr">
-        <is>
-          <t>₺940.000</t>
-        </is>
+      <c r="E7" s="256">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="159" t="n"/>
       <c r="G7" s="159" t="n"/>
-      <c r="H7" s="168" t="inlineStr">
-        <is>
-          <t>₺8.120.000</t>
-        </is>
+      <c r="H7" s="255">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="159" t="n"/>
       <c r="J7" s="159" t="n"/>
-      <c r="K7" s="170" t="inlineStr">
-        <is>
-          <t>98/100</t>
-        </is>
+      <c r="K7" s="170">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="159" t="n"/>
       <c r="M7" s="159" t="n"/>
@@ -26455,28 +26470,28 @@
     <row r="9">
       <c r="B9" s="171" t="inlineStr">
         <is>
-          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="159" t="n"/>
       <c r="D9" s="159" t="n"/>
       <c r="E9" s="172" t="inlineStr">
         <is>
-          <t>● Tüm riskli kayıtlar kontrol altında</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="159" t="n"/>
       <c r="G9" s="159" t="n"/>
       <c r="H9" s="171" t="inlineStr">
         <is>
-          <t>██████████░░░░░ %28.5 NET MARJ</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="159" t="n"/>
       <c r="J9" s="159" t="n"/>
       <c r="K9" s="173" t="inlineStr">
         <is>
-          <t>✓ 0 Formül ve Döngüsel Hata</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="159" t="n"/>
@@ -26485,7 +26500,7 @@
     <row r="11">
       <c r="B11" s="90" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>ASGARI ÜCRET ZAM ETKISI &amp; FIYAT AYARLAMA CETVELI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="174" t="inlineStr">
@@ -26502,7 +26517,7 @@
     <row r="12">
       <c r="B12" s="89" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="89" t="inlineStr">
@@ -26575,18 +26590,16 @@
       </c>
       <c r="H15" s="177" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="177" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="178" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="257">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="258">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="179" t="inlineStr">
         <is>
@@ -26616,18 +26629,16 @@
       </c>
       <c r="H16" s="177" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="177" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="178" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="257">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="258">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="179" t="inlineStr">
         <is>
@@ -26657,18 +26668,16 @@
       </c>
       <c r="H17" s="177" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="177" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="178" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="257">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="258">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="179" t="inlineStr">
         <is>
@@ -26698,18 +26707,16 @@
       </c>
       <c r="H18" s="177" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="177" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="178" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="257">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="258">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="179" t="inlineStr">
         <is>
@@ -26742,15 +26749,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="182" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="183" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="259">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="260">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="184" t="inlineStr"/>
       <c r="L19" s="185" t="inlineStr">
@@ -26812,7 +26817,7 @@
       </c>
       <c r="K23" s="190" t="inlineStr">
         <is>
-          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
         </is>
       </c>
       <c r="L23" s="188" t="n"/>
@@ -26836,7 +26841,7 @@
       </c>
       <c r="K24" s="191" t="inlineStr">
         <is>
-          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
         </is>
       </c>
     </row>
@@ -28897,7 +28902,7 @@
     <row r="3">
       <c r="B3" s="196" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  ASGARI ÜCRET ZAM ETKISI &amp; FIYAT AYARLAMA CETVELI — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="197" t="inlineStr">
@@ -28966,10 +28971,10 @@
       </c>
       <c r="D6" s="202" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="203" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="261" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="204" t="n">
@@ -29003,10 +29008,10 @@
       </c>
       <c r="D7" s="209" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="210" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="261" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="211" t="n">
@@ -29040,10 +29045,10 @@
       </c>
       <c r="D8" s="202" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="203" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="261" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="204" t="n">
@@ -29077,10 +29082,10 @@
       </c>
       <c r="D9" s="209" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="210" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="261" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="211" t="n">
@@ -29114,10 +29119,10 @@
       </c>
       <c r="D10" s="202" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="203" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="261" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="204" t="n">
@@ -29151,10 +29156,10 @@
       </c>
       <c r="D11" s="209" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="210" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="261" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="211" t="n">
@@ -29166,7 +29171,7 @@
       </c>
       <c r="H11" s="209" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="215" t="inlineStr">
@@ -29188,10 +29193,10 @@
       </c>
       <c r="D12" s="202" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="203" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="261" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="204" t="n">
@@ -29203,7 +29208,7 @@
       </c>
       <c r="H12" s="202" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="206" t="inlineStr">
@@ -29225,10 +29230,10 @@
       </c>
       <c r="D13" s="209" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="210" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="261" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="211" t="n">
@@ -29262,10 +29267,10 @@
       </c>
       <c r="D14" s="202" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="203" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="261" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="204" t="n">
@@ -29299,10 +29304,10 @@
       </c>
       <c r="D15" s="209" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="210" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="261" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="211" t="n">
@@ -29386,14 +29391,14 @@
     <row r="2">
       <c r="B2" s="218" t="inlineStr">
         <is>
-          <t>ASGARI UCRET ZAM ETKISI FIYAT AYARLAMA CETVELI — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>ASGARI ÜCRET ZAM ETKISI &amp; FIYAT AYARLAMA CETVELI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="219" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · KOBİ sahipleri, işletme yöneticileri, mali müşavirler, fiyatlandırma ve İK bütçesi yapan profesyoneller</t>
         </is>
       </c>
     </row>
@@ -29472,10 +29477,9 @@
       </c>
       <c r="C9" s="159" t="n"/>
       <c r="D9" s="159" t="n"/>
-      <c r="E9" s="226" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="262">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="159" t="n"/>
       <c r="H9" s="223" t="inlineStr">
@@ -29485,10 +29489,9 @@
       </c>
       <c r="I9" s="159" t="n"/>
       <c r="J9" s="159" t="n"/>
-      <c r="K9" s="226" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="262">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="159" t="n"/>
     </row>
@@ -29500,10 +29503,9 @@
       </c>
       <c r="C10" s="159" t="n"/>
       <c r="D10" s="159" t="n"/>
-      <c r="E10" s="227" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="263">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="159" t="n"/>
       <c r="H10" s="223" t="inlineStr">
@@ -29513,10 +29515,9 @@
       </c>
       <c r="I10" s="159" t="n"/>
       <c r="J10" s="159" t="n"/>
-      <c r="K10" s="227" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="263">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="159" t="n"/>
     </row>
@@ -29528,10 +29529,9 @@
       </c>
       <c r="C11" s="159" t="n"/>
       <c r="D11" s="159" t="n"/>
-      <c r="E11" s="227" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="264">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="159" t="n"/>
       <c r="H11" s="223" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/asgari-ucret-zam-etkisi-fiyat-ayarlama-cetveli/AsgariUcretZamEtkisiFiyatAyarlamaCetveli.xlsx
+++ b/EXCELARSIV_PRODUCTS/asgari-ucret-zam-etkisi-fiyat-ayarlama-cetveli/AsgariUcretZamEtkisiFiyatAyarlamaCetveli.xlsx
@@ -144,7 +144,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="97">
+  <fonts count="99">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -747,8 +747,20 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -944,6 +956,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1320,7 +1338,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="285">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2017,6 +2035,30 @@
     </xf>
     <xf numFmtId="170" fontId="79" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3476,20 +3518,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="66" min="1" max="1"/>
-    <col width="78" customWidth="1" style="66" min="2" max="2"/>
+    <col width="147.5" customWidth="1" style="66" min="2" max="2"/>
+    <col width="13" customWidth="1" style="66" min="3" max="3"/>
+    <col width="13" customWidth="1" style="66" min="4" max="4"/>
+    <col width="13" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="66">
-      <c r="A1" s="231" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
       <c r="A3" s="232" t="inlineStr">
         <is>
@@ -3754,6 +3813,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1" s="66">
       <c r="A26" s="235" t="inlineStr">
         <is>
@@ -3852,7 +3912,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3868,17 +3928,35 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="60" customWidth="1" style="92" min="1" max="3"/>
+    <col width="13" customWidth="1" style="66" min="2" max="2"/>
+    <col width="13" customWidth="1" style="66" min="3" max="3"/>
+    <col width="13" customWidth="1" style="66" min="4" max="4"/>
+    <col width="13" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5" customHeight="1" s="66">
-      <c r="A1" s="93" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1" s="66">
-      <c r="A3" s="94" t="inlineStr">
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="66">
+      <c r="A3" s="284" t="inlineStr">
         <is>
           <t>Asgari ücret zammının işletmenize maliyetini ölçün, fiyatlarınızı veriyle ayarlayın.</t>
         </is>
@@ -3913,6 +3991,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="66">
       <c r="A10" s="97" t="inlineStr">
         <is>
@@ -3923,6 +4002,7 @@
     <row r="11" ht="15" customHeight="1" s="66"/>
     <row r="12" ht="15" customHeight="1" s="66"/>
     <row r="13" ht="15" customHeight="1" s="66"/>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="66">
       <c r="A15" s="98" t="inlineStr">
         <is>
@@ -3943,11 +4023,11 @@
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A10:C13"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A4:C5"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3964,8 +4044,16 @@
   <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="72" customWidth="1" style="92" min="1" max="1"/>
+    <col width="129.5" customWidth="1" style="92" min="1" max="1"/>
     <col width="20" customWidth="1" style="92" min="2" max="2"/>
+    <col width="13" customWidth="1" style="66" min="3" max="3"/>
+    <col width="13" customWidth="1" style="66" min="4" max="4"/>
+    <col width="13" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3975,8 +4063,9 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="66">
-      <c r="A3" s="100" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="66">
+      <c r="A3" s="284" t="inlineStr">
         <is>
           <t>Nasıl kullanılır?</t>
         </is>
@@ -4031,6 +4120,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="66">
       <c r="A12" s="102" t="inlineStr">
         <is>
@@ -4073,6 +4163,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="19.5" customHeight="1" s="66">
       <c r="A19" s="103" t="inlineStr">
         <is>
@@ -4082,7 +4173,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A8:AN8"/>
     <mergeCell ref="A6:AN6"/>
     <mergeCell ref="A4:AN4"/>
@@ -4092,6 +4183,7 @@
     <mergeCell ref="A19:AN19"/>
     <mergeCell ref="A10:AN10"/>
     <mergeCell ref="A5:AN5"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A13:AN13"/>
     <mergeCell ref="A14:AN14"/>
     <mergeCell ref="A17:AN17"/>
@@ -4113,26 +4205,41 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="92" min="1" max="1"/>
-    <col width="16" customWidth="1" style="92" min="2" max="2"/>
-    <col width="18" customWidth="1" style="92" min="3" max="3"/>
+    <col width="20.5" customWidth="1" style="92" min="2" max="2"/>
+    <col width="29.5" customWidth="1" style="92" min="3" max="3"/>
     <col width="20" customWidth="1" style="92" min="4" max="4"/>
-    <col width="12" customWidth="1" style="92" min="5" max="5"/>
-    <col width="14" customWidth="1" style="92" min="6" max="6"/>
-    <col width="18" customWidth="1" style="92" min="7" max="9"/>
-    <col width="16" customWidth="1" style="92" min="10" max="10"/>
-    <col width="14" customWidth="1" style="92" min="11" max="11"/>
-    <col width="12" customWidth="1" style="92" min="12" max="12"/>
+    <col width="17.5" customWidth="1" style="92" min="5" max="5"/>
+    <col width="21.5" customWidth="1" style="92" min="6" max="6"/>
+    <col width="30.5" customWidth="1" style="92" min="7" max="9"/>
+    <col width="35.5" customWidth="1" style="66" min="8" max="8"/>
+    <col width="36.5" customWidth="1" style="66" min="9" max="9"/>
+    <col width="21.5" customWidth="1" style="92" min="10" max="10"/>
+    <col width="23.5" customWidth="1" style="92" min="11" max="11"/>
+    <col width="14.5" customWidth="1" style="92" min="12" max="12"/>
+    <col width="13" customWidth="1" style="66" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>CALISANLAR — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="66">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+      <c r="J1" s="266" t="n"/>
+      <c r="K1" s="266" t="n"/>
+      <c r="L1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="66">
+      <c r="A3" s="284" t="inlineStr">
         <is>
           <t>Çalışan Girişi (Zam Öncesi/Sonrası Maliyet)</t>
         </is>
@@ -11816,6 +11923,7 @@
       <c r="D1004" s="113" t="n"/>
       <c r="E1004" s="113" t="n"/>
     </row>
+    <row r="1005"/>
     <row r="1006" ht="19.5" customHeight="1" s="66">
       <c r="A1006" s="103" t="inlineStr">
         <is>
@@ -11825,8 +11933,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="3">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:L3"/>
     <mergeCell ref="A1006:AN1006"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
@@ -11885,21 +11994,35 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="92" min="1" max="1"/>
-    <col width="18" customWidth="1" style="92" min="2" max="3"/>
-    <col width="14" customWidth="1" style="92" min="4" max="5"/>
-    <col width="16" customWidth="1" style="92" min="6" max="6"/>
-    <col width="18" customWidth="1" style="92" min="7" max="9"/>
+    <col width="26.5" customWidth="1" style="92" min="2" max="3"/>
+    <col width="28.5" customWidth="1" style="66" min="3" max="3"/>
+    <col width="14.5" customWidth="1" style="92" min="4" max="5"/>
+    <col width="17.5" customWidth="1" style="66" min="5" max="5"/>
+    <col width="24.5" customWidth="1" style="92" min="6" max="6"/>
+    <col width="27.5" customWidth="1" style="92" min="7" max="9"/>
+    <col width="33.5" customWidth="1" style="66" min="8" max="8"/>
+    <col width="26.5" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>URUNLER — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="66">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="66">
+      <c r="A3" s="284" t="inlineStr">
         <is>
           <t>Ürün/Hizmet Fiyat Ayarlama Cetveli</t>
         </is>
@@ -24253,6 +24376,7 @@
       <c r="C2004" s="113" t="n"/>
       <c r="D2004" s="113" t="n"/>
     </row>
+    <row r="2005"/>
     <row r="2006" ht="19.5" customHeight="1" s="66">
       <c r="A2006" s="103" t="inlineStr">
         <is>
@@ -24262,10 +24386,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A2006:AN2006"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F2004">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
@@ -24312,17 +24437,33 @@
     <col width="46" customWidth="1" style="92" min="1" max="1"/>
     <col width="20" customWidth="1" style="92" min="2" max="2"/>
     <col width="78" customWidth="1" style="92" min="3" max="3"/>
+    <col width="13" customWidth="1" style="66" min="4" max="4"/>
+    <col width="13" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>MOTOR — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="66">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="66">
+      <c r="A3" s="284" t="inlineStr">
         <is>
           <t>Hesaplama Motoru</t>
         </is>
@@ -24335,6 +24476,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="66">
       <c r="A6" s="115" t="inlineStr">
         <is>
@@ -24518,6 +24660,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="66">
       <c r="A24" s="105" t="inlineStr">
         <is>
@@ -24958,10 +25101,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A58:AN58"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="B13">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
@@ -25005,25 +25148,42 @@
   <dimension ref="A1:AN26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="46" customWidth="1" style="92" min="1" max="1"/>
-    <col width="22" customWidth="1" style="92" min="2" max="2"/>
+    <col width="63.5" customWidth="1" style="92" min="1" max="1"/>
+    <col width="47.5" customWidth="1" style="92" min="2" max="2"/>
     <col width="40" customWidth="1" style="92" min="3" max="3"/>
+    <col width="13" customWidth="1" style="66" min="4" max="4"/>
+    <col width="13" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>KONTROL — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="66">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="66">
+      <c r="A3" s="284" t="inlineStr">
         <is>
           <t>Veri Kalite Kontrolleri</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="66">
       <c r="A5" s="116" t="inlineStr">
         <is>
@@ -25112,6 +25272,8 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="66">
       <c r="A15" s="115" t="inlineStr">
         <is>
@@ -25218,6 +25380,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="19.5" customHeight="1" s="66">
       <c r="A26" s="103" t="inlineStr">
         <is>
@@ -25228,9 +25391,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A26:AN26"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B12">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
@@ -25277,18 +25440,34 @@
   <dimension ref="A1:AN21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="46" customWidth="1" style="92" min="1" max="1"/>
+    <col width="101.5" customWidth="1" style="92" min="1" max="1"/>
     <col width="28" customWidth="1" style="92" min="2" max="2"/>
     <col width="22" customWidth="1" style="92" min="3" max="3"/>
+    <col width="13" customWidth="1" style="66" min="4" max="4"/>
+    <col width="13" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>KARAR — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="66">
       <c r="A3" s="105" t="inlineStr">
         <is>
@@ -25296,6 +25475,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="66">
       <c r="A5" s="115" t="inlineStr">
         <is>
@@ -25347,6 +25527,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="18.75" customHeight="1" s="66">
       <c r="A11" s="105" t="inlineStr">
         <is>
@@ -25369,6 +25550,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="66">
       <c r="A14" s="115" t="inlineStr">
         <is>
@@ -25400,6 +25582,8 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21" ht="19.5" customHeight="1" s="66">
       <c r="A21" s="103" t="inlineStr">
         <is>
@@ -25413,9 +25597,9 @@
     <mergeCell ref="A21:AN21"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="B11">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
@@ -25461,22 +25645,43 @@
   <cols>
     <col width="46" customWidth="1" style="92" min="1" max="1"/>
     <col width="20" customWidth="1" style="92" min="2" max="4"/>
+    <col width="13" customWidth="1" style="66" min="3" max="3"/>
+    <col width="13" customWidth="1" style="66" min="4" max="4"/>
+    <col width="13" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
+    <col width="13" customWidth="1" style="66" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>SENARYO DUYARLILIK — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="66">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+      <c r="J1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="66">
+      <c r="A3" s="284" t="inlineStr">
         <is>
           <t>Senaryo ve Duyarlılık Analizi</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1" s="66">
       <c r="A6" s="107" t="inlineStr">
         <is>
@@ -25594,6 +25799,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="66">
       <c r="A13" s="115" t="inlineStr">
         <is>
@@ -25639,6 +25845,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="66">
       <c r="A17" s="122" t="inlineStr">
         <is>
@@ -25650,6 +25857,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="19.5" customHeight="1" s="66">
       <c r="A19" s="103" t="inlineStr">
         <is>
@@ -25659,9 +25867,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A19:AN19"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="B7:D10">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
@@ -25688,17 +25897,32 @@
   <dimension ref="A1:AD37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="42" customWidth="1" style="92" min="1" max="1"/>
+    <col width="107.5" customWidth="1" style="92" min="1" max="1"/>
     <col width="26" customWidth="1" style="92" min="2" max="2"/>
     <col width="30" customWidth="1" style="92" min="3" max="3"/>
+    <col width="13" customWidth="1" style="66" min="4" max="4"/>
+    <col width="13" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>RAPOR — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2" ht="24.75" customHeight="1" s="66">
       <c r="A2" s="138" t="inlineStr">
@@ -25747,6 +25971,7 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="15" customHeight="1" s="66">
       <c r="A8" s="115" t="inlineStr">
         <is>
@@ -25842,6 +26067,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="66">
       <c r="A18" s="142">
         <f>KararGerekce</f>
@@ -25877,6 +26103,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="15" customHeight="1" s="66">
       <c r="A25" s="115" t="inlineStr">
         <is>
@@ -25905,6 +26132,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="66">
       <c r="A30" s="115" t="inlineStr">
         <is>
@@ -25933,6 +26161,8 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36" ht="15" customHeight="1" s="66">
       <c r="A36" s="99" t="inlineStr">
         <is>
@@ -25960,10 +26190,10 @@
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
@@ -26012,27 +26242,42 @@
   <dimension ref="A1:AN22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="24" customWidth="1" style="92" min="1" max="1"/>
-    <col width="16" customWidth="1" style="92" min="2" max="2"/>
-    <col width="18" customWidth="1" style="92" min="3" max="3"/>
+    <col width="74.5" customWidth="1" style="92" min="1" max="1"/>
+    <col width="26.5" customWidth="1" style="92" min="2" max="2"/>
+    <col width="29.5" customWidth="1" style="92" min="3" max="3"/>
     <col width="20" customWidth="1" style="92" min="4" max="4"/>
-    <col width="12" customWidth="1" style="92" min="5" max="5"/>
+    <col width="17.5" customWidth="1" style="92" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>ORNEK VERI — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="66">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="66">
+      <c r="A3" s="284" t="inlineStr">
         <is>
           <t>Örnek Veri (CALISANLAR)</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="66">
       <c r="A5" s="107" t="inlineStr">
         <is>
@@ -26198,6 +26443,8 @@
         <v>0.12</v>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="66">
       <c r="A14" s="105" t="inlineStr">
         <is>
@@ -26205,6 +26452,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="30" customHeight="1" s="66">
       <c r="A16" s="107" t="inlineStr">
         <is>
@@ -26292,6 +26540,7 @@
         <v>40</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="19.5" customHeight="1" s="66">
       <c r="A22" s="103" t="inlineStr">
         <is>
@@ -26301,9 +26550,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A22:AN22"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -26318,22 +26568,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="66" min="1" max="1"/>
-    <col width="18" customWidth="1" style="66" min="2" max="2"/>
+    <col width="83.5" customWidth="1" style="66" min="2" max="2"/>
     <col width="15" customWidth="1" style="66" min="3" max="3"/>
-    <col width="12" customWidth="1" style="66" min="4" max="4"/>
-    <col width="16" customWidth="1" style="66" min="5" max="5"/>
+    <col width="15.5" customWidth="1" style="66" min="4" max="4"/>
+    <col width="36.5" customWidth="1" style="66" min="5" max="5"/>
     <col width="18" customWidth="1" style="66" min="6" max="6"/>
-    <col width="6" customWidth="1" style="66" min="7" max="7"/>
-    <col width="24" customWidth="1" style="66" min="8" max="8"/>
+    <col width="11.5" customWidth="1" style="66" min="7" max="7"/>
+    <col width="75.5" customWidth="1" style="66" min="8" max="8"/>
     <col width="15" customWidth="1" style="66" min="9" max="9"/>
-    <col width="15" customWidth="1" style="66" min="10" max="10"/>
-    <col width="12" customWidth="1" style="66" min="11" max="11"/>
+    <col width="15.5" customWidth="1" style="66" min="10" max="10"/>
+    <col width="81.5" customWidth="1" style="66" min="11" max="11"/>
     <col width="18" customWidth="1" style="66" min="12" max="12"/>
     <col width="18" customWidth="1" style="66" min="13" max="13"/>
+    <col width="13" customWidth="1" style="66" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26367,6 +26618,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="158" t="inlineStr">
         <is>
@@ -26497,6 +26749,7 @@
       <c r="L9" s="159" t="n"/>
       <c r="M9" s="159" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="90" t="inlineStr">
         <is>
@@ -26526,6 +26779,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="175" t="inlineStr">
         <is>
@@ -26780,6 +27034,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="186" t="inlineStr">
         <is>
@@ -26868,13 +27123,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="267" t="n"/>
+      <c r="H26" s="267" t="n"/>
+      <c r="I26" s="268" t="n"/>
       <c r="K26" s="195" t="inlineStr">
         <is>
           <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="269" t="n"/>
+      <c r="G27" s="270" t="n"/>
+      <c r="H27" s="270" t="n"/>
+      <c r="I27" s="271" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -26891,24 +27154,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="92" min="1" max="1"/>
+    <col width="16.5" customWidth="1" style="92" min="1" max="1"/>
     <col width="16" customWidth="1" style="92" min="2" max="2"/>
     <col width="14" customWidth="1" style="92" min="3" max="4"/>
+    <col width="13" customWidth="1" style="66" min="4" max="4"/>
     <col width="10" customWidth="1" style="92" min="5" max="5"/>
-    <col width="14" customWidth="1" style="92" min="6" max="6"/>
-    <col width="40" customWidth="1" style="92" min="7" max="7"/>
+    <col width="16.5" customWidth="1" style="92" min="6" max="6"/>
+    <col width="40.5" customWidth="1" style="92" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="66">
-      <c r="A1" s="92" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>AKIS — AsgariUcretZamEtkisiFiyatAyarlamaCetveli</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="66">
       <c r="A3" s="92" t="inlineStr">
         <is>
@@ -27086,6 +27362,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="66">
       <c r="A9" s="92" t="inlineStr">
         <is>
@@ -27099,6 +27376,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -27116,23 +27396,40 @@
   <cols>
     <col width="14" customWidth="1" style="92" min="1" max="1"/>
     <col width="20" customWidth="1" style="92" min="2" max="2"/>
-    <col width="50" customWidth="1" style="92" min="3" max="3"/>
+    <col width="98.5" customWidth="1" style="92" min="3" max="3"/>
+    <col width="13" customWidth="1" style="66" min="4" max="4"/>
+    <col width="13" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>DEGISIKLIK KAYDI — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="66">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="66">
+      <c r="A3" s="284" t="inlineStr">
         <is>
           <t>Değişiklik Kaydı</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="66">
       <c r="A5" s="107" t="inlineStr">
         <is>
@@ -27169,8 +27466,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -27188,17 +27486,35 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="92" min="1" max="3"/>
+    <col width="13" customWidth="1" style="66" min="2" max="2"/>
+    <col width="13" customWidth="1" style="66" min="3" max="3"/>
+    <col width="13" customWidth="1" style="66" min="4" max="4"/>
+    <col width="13" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>LISTELER — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="66">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="66">
+      <c r="A3" s="284" t="inlineStr">
         <is>
           <t>Açılır Liste Kaynakları</t>
         </is>
@@ -27211,6 +27527,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="66">
       <c r="A6" s="145" t="inlineStr">
         <is>
@@ -27232,6 +27549,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="19.5" customHeight="1" s="66">
       <c r="A11" s="103" t="inlineStr">
         <is>
@@ -27241,9 +27560,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A11:AN11"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -27261,13 +27581,15 @@
   <dimension ref="A1:AN44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="30" customWidth="1" style="92" min="1" max="1"/>
+    <col width="92.5" customWidth="1" style="92" min="1" max="1"/>
     <col width="26" customWidth="1" style="92" min="2" max="2"/>
-    <col width="16" customWidth="1" style="92" min="3" max="3"/>
-    <col width="10" customWidth="1" style="92" min="4" max="4"/>
-    <col width="62" customWidth="1" style="92" min="5" max="5"/>
-    <col width="28" customWidth="1" style="92" min="6" max="6"/>
-    <col width="14" customWidth="1" style="92" min="7" max="8"/>
+    <col width="21.5" customWidth="1" style="92" min="3" max="3"/>
+    <col width="11.5" customWidth="1" style="92" min="4" max="4"/>
+    <col width="72.5" customWidth="1" style="92" min="5" max="5"/>
+    <col width="63.5" customWidth="1" style="92" min="6" max="6"/>
+    <col width="19.5" customWidth="1" style="92" min="7" max="8"/>
+    <col width="20.5" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
     <col width="16" customWidth="1" style="92" min="10" max="10"/>
     <col width="13" customWidth="1" style="92" min="11" max="11"/>
     <col width="28" customWidth="1" style="92" min="12" max="12"/>
@@ -27275,15 +27597,23 @@
     <col width="13" customWidth="1" style="92" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>AYARLAR — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="66">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="66">
+      <c r="A3" s="284" t="inlineStr">
         <is>
           <t>Ayarlar ve Eşikler (Formüle Sabit Sayı Girilmez)</t>
         </is>
@@ -28581,6 +28911,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38" ht="19.5" customHeight="1" s="66">
       <c r="A38" s="103" t="inlineStr">
         <is>
@@ -28588,6 +28919,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="15" customHeight="1" s="66">
       <c r="J40" s="92" t="inlineStr">
         <is>
@@ -28728,8 +29060,8 @@
   <mergeCells count="4">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
     <mergeCell ref="A38:AN38"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -28747,23 +29079,42 @@
   <dimension ref="A1:BH18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="90" customWidth="1" style="92" min="1" max="1"/>
+    <col width="129.5" customWidth="1" style="92" min="1" max="1"/>
+    <col width="13" customWidth="1" style="66" min="2" max="2"/>
+    <col width="13" customWidth="1" style="66" min="3" max="3"/>
+    <col width="13" customWidth="1" style="66" min="4" max="4"/>
+    <col width="13" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="66">
-      <c r="A1" s="104" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>KILAVUZ — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" s="66">
-      <c r="A3" s="100" t="inlineStr">
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="66">
+      <c r="A3" s="284" t="inlineStr">
         <is>
           <t>Kullanım Kılavuzu</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="66">
       <c r="A5" s="101" t="inlineStr">
         <is>
@@ -28841,6 +29192,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18" ht="19.5" customHeight="1" s="66">
       <c r="A18" s="103" t="inlineStr">
         <is>
@@ -28850,7 +29203,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A12:BH12"/>
     <mergeCell ref="A7:BH7"/>
     <mergeCell ref="A15:BH15"/>
@@ -28858,11 +29211,12 @@
     <mergeCell ref="A13:BH13"/>
     <mergeCell ref="A11:BH11"/>
     <mergeCell ref="A14:BH14"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A5:BH5"/>
     <mergeCell ref="A8:BH8"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A6:BH6"/>
     <mergeCell ref="A9:BH9"/>
-    <mergeCell ref="A1:AD1"/>
     <mergeCell ref="A18:AN18"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -28878,18 +29232,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="66" min="1" max="1"/>
-    <col width="14" customWidth="1" style="66" min="2" max="2"/>
+    <col width="36.5" customWidth="1" style="66" min="2" max="2"/>
     <col width="16" customWidth="1" style="66" min="3" max="3"/>
-    <col width="32" customWidth="1" style="66" min="4" max="4"/>
-    <col width="18" customWidth="1" style="66" min="5" max="5"/>
-    <col width="12" customWidth="1" style="66" min="6" max="6"/>
+    <col width="37.5" customWidth="1" style="66" min="4" max="4"/>
+    <col width="18.5" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13.5" customWidth="1" style="66" min="6" max="6"/>
     <col width="18" customWidth="1" style="66" min="7" max="7"/>
-    <col width="22" customWidth="1" style="66" min="8" max="8"/>
+    <col width="22.5" customWidth="1" style="66" min="8" max="8"/>
     <col width="16" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28899,12 +29254,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="196" t="inlineStr">
         <is>
           <t>🔍  ASGARI ÜCRET ZAM ETKISI &amp; FIYAT AYARLAMA CETVELI — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="272" t="n"/>
+      <c r="D3" s="272" t="n"/>
+      <c r="E3" s="273" t="n"/>
       <c r="G3" s="197" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -28916,6 +29275,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="199" t="inlineStr">
         <is>
@@ -29328,22 +29688,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="216" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="184" t="n"/>
-      <c r="D17" s="184" t="n"/>
       <c r="E17" s="217">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="184" t="n"/>
-      <c r="G17" s="184" t="n"/>
-      <c r="H17" s="184" t="n"/>
-      <c r="I17" s="184" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -29364,7 +29719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="66" min="1" max="1"/>
@@ -29409,25 +29764,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="221" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="159" t="n"/>
-      <c r="D6" s="159" t="n"/>
-      <c r="E6" s="159" t="n"/>
-      <c r="F6" s="159" t="n"/>
+      <c r="C6" s="272" t="n"/>
+      <c r="D6" s="272" t="n"/>
+      <c r="E6" s="272" t="n"/>
+      <c r="F6" s="273" t="n"/>
       <c r="H6" s="222" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="159" t="n"/>
-      <c r="J6" s="159" t="n"/>
-      <c r="K6" s="159" t="n"/>
-      <c r="L6" s="159" t="n"/>
+      <c r="I6" s="272" t="n"/>
+      <c r="J6" s="272" t="n"/>
+      <c r="K6" s="272" t="n"/>
+      <c r="L6" s="273" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="159" t="n"/>
@@ -29578,32 +29934,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="159" t="n"/>
-      <c r="D14" s="159" t="n"/>
-      <c r="E14" s="159" t="n"/>
-      <c r="F14" s="159" t="n"/>
+      <c r="C14" s="274" t="n"/>
+      <c r="D14" s="274" t="n"/>
+      <c r="E14" s="274" t="n"/>
+      <c r="F14" s="275" t="n"/>
       <c r="H14" s="229" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="159" t="n"/>
-      <c r="J14" s="159" t="n"/>
-      <c r="K14" s="159" t="n"/>
-      <c r="L14" s="159" t="n"/>
+      <c r="I14" s="276" t="n"/>
+      <c r="J14" s="276" t="n"/>
+      <c r="K14" s="276" t="n"/>
+      <c r="L14" s="277" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="159" t="n"/>
-      <c r="C15" s="159" t="n"/>
-      <c r="D15" s="159" t="n"/>
-      <c r="E15" s="159" t="n"/>
-      <c r="F15" s="159" t="n"/>
-      <c r="H15" s="159" t="n"/>
-      <c r="I15" s="159" t="n"/>
-      <c r="J15" s="159" t="n"/>
-      <c r="K15" s="159" t="n"/>
-      <c r="L15" s="159" t="n"/>
-    </row>
+      <c r="B15" s="278" t="n"/>
+      <c r="C15" s="279" t="n"/>
+      <c r="D15" s="279" t="n"/>
+      <c r="E15" s="279" t="n"/>
+      <c r="F15" s="280" t="n"/>
+      <c r="H15" s="281" t="n"/>
+      <c r="I15" s="282" t="n"/>
+      <c r="J15" s="282" t="n"/>
+      <c r="K15" s="282" t="n"/>
+      <c r="L15" s="283" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="77" t="inlineStr">
         <is>
@@ -29611,6 +29968,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="186" t="inlineStr">
         <is>
@@ -29685,25 +30043,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="66" min="1" max="1"/>
-    <col width="24" customWidth="1" style="66" min="2" max="2"/>
-    <col width="22" customWidth="1" style="66" min="3" max="3"/>
-    <col width="27" customWidth="1" style="66" min="4" max="4"/>
-    <col width="29" customWidth="1" style="66" min="5" max="5"/>
-    <col width="20" customWidth="1" style="66" min="6" max="6"/>
+    <col width="30.5" customWidth="1" style="66" min="2" max="2"/>
+    <col width="23.5" customWidth="1" style="66" min="3" max="3"/>
+    <col width="48.5" customWidth="1" style="66" min="4" max="4"/>
+    <col width="43.5" customWidth="1" style="66" min="5" max="5"/>
+    <col width="21.5" customWidth="1" style="66" min="6" max="6"/>
     <col width="21" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="66">
-      <c r="A1" s="236" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
       <c r="A3" s="237" t="inlineStr">
         <is>
@@ -30163,7 +30533,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30176,22 +30546,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="66" min="1" max="1"/>
-    <col width="52" customWidth="1" style="66" min="2" max="2"/>
-    <col width="34" customWidth="1" style="66" min="3" max="3"/>
+    <col width="89.5" customWidth="1" style="66" min="2" max="2"/>
+    <col width="34.5" customWidth="1" style="66" min="3" max="3"/>
     <col width="16" customWidth="1" style="66" min="4" max="4"/>
+    <col width="13" customWidth="1" style="66" min="5" max="5"/>
+    <col width="13" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="66">
-      <c r="A1" s="239" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
       <c r="A3" s="240" t="inlineStr">
         <is>
@@ -30903,7 +31288,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30916,24 +31301,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" style="66" min="1" max="1"/>
-    <col width="36" customWidth="1" style="66" min="2" max="2"/>
-    <col width="48" customWidth="1" style="66" min="3" max="3"/>
-    <col width="34" customWidth="1" style="66" min="4" max="4"/>
-    <col width="30" customWidth="1" style="66" min="5" max="5"/>
+    <col width="30.5" customWidth="1" style="66" min="1" max="1"/>
+    <col width="71.5" customWidth="1" style="66" min="2" max="2"/>
+    <col width="160.5" customWidth="1" style="66" min="3" max="3"/>
+    <col width="70.5" customWidth="1" style="66" min="4" max="4"/>
+    <col width="50.5" customWidth="1" style="66" min="5" max="5"/>
     <col width="16" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="66">
-      <c r="A1" s="244" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
       <c r="A3" s="245" t="inlineStr">
         <is>
@@ -31576,7 +31974,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31589,24 +31987,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="66" min="1" max="1"/>
-    <col width="40" customWidth="1" style="66" min="2" max="2"/>
-    <col width="50" customWidth="1" style="66" min="3" max="3"/>
-    <col width="30" customWidth="1" style="66" min="4" max="4"/>
-    <col width="28" customWidth="1" style="66" min="5" max="5"/>
-    <col width="26" customWidth="1" style="66" min="6" max="6"/>
+    <col width="22.5" customWidth="1" style="66" min="1" max="1"/>
+    <col width="60.5" customWidth="1" style="66" min="2" max="2"/>
+    <col width="86.5" customWidth="1" style="66" min="3" max="3"/>
+    <col width="40.5" customWidth="1" style="66" min="4" max="4"/>
+    <col width="39.5" customWidth="1" style="66" min="5" max="5"/>
+    <col width="27.5" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="66">
-      <c r="A1" s="248" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
       <c r="A3" s="249" t="inlineStr">
         <is>
@@ -32121,7 +32532,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -32134,23 +32545,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="66" min="1" max="1"/>
-    <col width="32" customWidth="1" style="66" min="2" max="2"/>
-    <col width="54" customWidth="1" style="66" min="3" max="3"/>
-    <col width="34" customWidth="1" style="66" min="4" max="4"/>
+    <col width="20.5" customWidth="1" style="66" min="1" max="1"/>
+    <col width="41.5" customWidth="1" style="66" min="2" max="2"/>
+    <col width="86.5" customWidth="1" style="66" min="3" max="3"/>
+    <col width="35.5" customWidth="1" style="66" min="4" max="4"/>
+    <col width="33.5" customWidth="1" style="66" min="5" max="5"/>
     <col width="16" customWidth="1" style="66" min="6" max="6"/>
+    <col width="13" customWidth="1" style="66" min="7" max="7"/>
+    <col width="13" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="13" customWidth="1" style="66" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="66">
-      <c r="A1" s="251" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="66">
+      <c r="A1" s="265" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="266" t="n"/>
+      <c r="C1" s="266" t="n"/>
+      <c r="D1" s="266" t="n"/>
+      <c r="E1" s="266" t="n"/>
+      <c r="F1" s="266" t="n"/>
+      <c r="G1" s="266" t="n"/>
+      <c r="H1" s="266" t="n"/>
+      <c r="I1" s="266" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
       <c r="A3" s="252" t="inlineStr">
         <is>
@@ -32697,7 +33122,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/asgari-ucret-zam-etkisi-fiyat-ayarlama-cetveli/AsgariUcretZamEtkisiFiyatAyarlamaCetveli.xlsx
+++ b/EXCELARSIV_PRODUCTS/asgari-ucret-zam-etkisi-fiyat-ayarlama-cetveli/AsgariUcretZamEtkisiFiyatAyarlamaCetveli.xlsx
@@ -3518,7 +3518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="66" min="1" max="1"/>
@@ -3539,14 +3539,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
@@ -3924,7 +3916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="60" customWidth="1" style="92" min="1" max="3"/>
@@ -3945,14 +3937,6 @@
           <t>ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
@@ -4225,17 +4209,6 @@
           <t>CALISANLAR — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
-      <c r="J1" s="266" t="n"/>
-      <c r="K1" s="266" t="n"/>
-      <c r="L1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
@@ -11934,9 +11907,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="4">
-    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A3:L3"/>
     <mergeCell ref="A1006:AN1006"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J1004">
@@ -12011,14 +11984,6 @@
           <t>URUNLER — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
@@ -24388,9 +24353,9 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A2006:AN2006"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F2004">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
@@ -24452,14 +24417,6 @@
           <t>MOTOR — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
@@ -24862,7 +24819,7 @@
         <v/>
       </c>
       <c r="C42" s="120">
-        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"T1: Ortalama kıdem "&amp;modulT1KidemOrt&amp;" gün",IF(modulT1KidemOrt&gt;KidemSinirGun,"kıdem "&amp;KidemSinirGun/365&amp;" yıl üzerinde, kıdem tazminatı yükü yüksek","kıdem dağılımı normal"))</f>
+        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"T1: AVERAGE kıdem "&amp;modulT1KidemOrt&amp;" gün",IF(modulT1KidemOrt&gt;KidemSinirGun,"kıdem "&amp;KidemSinirGun/365&amp;" yıl üzerinde, kıdem tazminatı yükü yüksek","kıdem dağılımı normal"))</f>
         <v/>
       </c>
     </row>
@@ -24937,7 +24894,7 @@
         <v/>
       </c>
       <c r="C47" s="120">
-        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"T6: Ortalama işçilik oranı %"&amp;TEXT(modulT6BasabasUcretYuku*100,"0")&amp;"",IF(modulT6BasabasUcretYuku&gt;FiyatYansitmaEsik,"işçilik yoğun işletme, yansıtma kritik","işçilik oranı düşük"))</f>
+        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"T6: AVERAGE işçilik oranı %"&amp;TEXT(modulT6BasabasUcretYuku*100,"0")&amp;"",IF(modulT6BasabasUcretYuku&gt;FiyatYansitmaEsik,"işçilik yoğun işletme, yansıtma kritik","işçilik oranı düşük"))</f>
         <v/>
       </c>
     </row>
@@ -25102,9 +25059,9 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A58:AN58"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B13">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
@@ -25166,14 +25123,6 @@
           <t>KONTROL — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
@@ -25458,14 +25407,6 @@
           <t>KARAR — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="66">
@@ -25546,7 +25487,7 @@
         </is>
       </c>
       <c r="B12" s="126">
-        <f>IF(VeriKaliteSkoru=0,"Girdi eksik; lütfen sarı hücreleri doldurun.",IF(MaliyetArtisOrani&lt;0,"Maliyet artışı negatif: ücret ve fiyat girişlerini kontrol edin.",IF(MaliyetArtisOrani&gt;FiyatYansitmaEsik,"Maliyet artışı %"&amp;TEXT(MaliyetArtisOrani,"0.0%")&amp;" eşiği aşıyor; fiyat yansıtması zorunlu.",IF(modulI7AcikKopru&gt;0,"Fiyat yansıtması maliyet artışını karşılamıyor; açık "&amp;TEXT(modulI7AcikKopru,"#,##0")&amp;" ₺.",IF(ABS(modulT5MutabakatFark)&gt;ZamOncesiIsverenMaliyeti*MaliyetArtisEsik,"Ürün işçilik yükü ile fiili maliyet farkı yüksek; maliyet dağılımını denetleyin.","Maliyet artışı eşikler içinde; fiyat güncellemesi planlanabilir.")))))</f>
+        <f>IF(VeriKaliteSkoru=0,"Girdi eksik; lütfen sarı hücreleri doldurun.",IF(MaliyetArtisOrani&lt;0,"Maliyet artışı negatif: ücret AND fiyat girişlerini kontrol edin.",IF(MaliyetArtisOrani&gt;FiyatYansitmaEsik,"Maliyet artışı %"&amp;TEXT(MaliyetArtisOrani,"0.0%")&amp;" eşiği aşıyor; fiyat yansıtması zorunlu.",IF(modulI7AcikKopru&gt;0,"Fiyat yansıtması maliyet artışını karşılamıyor; açık "&amp;TEXT(modulI7AcikKopru,"#,##0")&amp;" ₺.",IF(ABS(modulT5MutabakatFark)&gt;ZamOncesiIsverenMaliyeti*MaliyetArtisEsik,"Ürün işçilik yükü ile fiili maliyet farkı yüksek; maliyet dağılımını denetleyin.","Maliyet artışı eşikler içinde; fiyat güncellemesi planlanabilir.")))))</f>
         <v/>
       </c>
     </row>
@@ -25560,7 +25501,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" s="66">
       <c r="A15" s="126">
-        <f>IF(OR(KararSonuc="VERİ YOK",KararSonuc="DURDUR"),"Ücret ve fiyat girişlerini tamamlayın; yansıtma açığını kapatmak için fiyat cetvelini gözden geçirin",IF(MaliyetArtisOrani&gt;MaliyetArtisEsik,"Maliyet artışı eşik üstünde; fiyat güncellemesini planlayın","Fiyat güncelleme planını sürdürün"))</f>
+        <f>IF(OR(KararSonuc="VERİ YOK",KararSonuc="DURDUR"),"Ücret AND fiyat girişlerini tamamlayın; yansıtma açığını kapatmak için fiyat cetvelini gözden geçirin",IF(MaliyetArtisOrani&gt;MaliyetArtisEsik,"Maliyet artışı eşik üstünde; fiyat güncellemesini planlayın","Fiyat güncelleme planını sürdürün"))</f>
         <v/>
       </c>
     </row>
@@ -25572,7 +25513,7 @@
     </row>
     <row r="17" ht="15" customHeight="1" s="66">
       <c r="A17" s="126">
-        <f>IF(AnomaliCalisanAdedi&gt;0,"Uç ücretli çalışanların ücret ve kıdem kayıtlarını inceleyin","Ücret dağılımı tutarlı")</f>
+        <f>IF(AnomaliCalisanAdedi&gt;0,"Uç ücretli çalışanların ücret AND kıdem kayıtlarını inceleyin","Ücret dağılımı tutarlı")</f>
         <v/>
       </c>
     </row>
@@ -25596,8 +25537,8 @@
   <mergeCells count="6">
     <mergeCell ref="A21:AN21"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A16:C16"/>
   </mergeCells>
@@ -25662,15 +25603,6 @@
           <t>SENARYO DUYARLILIK — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
-      <c r="J1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
@@ -25894,7 +25826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD37"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="107.5" customWidth="1" style="92" min="1" max="1"/>
@@ -25915,14 +25847,6 @@
           <t>RAPOR — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2" ht="24.75" customHeight="1" s="66">
       <c r="A2" s="138" t="inlineStr">
@@ -26260,14 +26184,6 @@
           <t>ORNEK VERI — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
@@ -26568,7 +26484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="66" min="1" max="1"/>
@@ -26699,7 +26615,7 @@
       <c r="I7" s="159" t="n"/>
       <c r="J7" s="159" t="n"/>
       <c r="K7" s="170">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="159" t="n"/>
@@ -27004,11 +26920,11 @@
         </is>
       </c>
       <c r="I19" s="259">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="260">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="184" t="inlineStr"/>
@@ -27154,7 +27070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.5" customWidth="1" style="92" min="1" max="1"/>
@@ -27175,14 +27091,6 @@
           <t>AKIS — AsgariUcretZamEtkisiFiyatAyarlamaCetveli</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="66">
@@ -27391,7 +27299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="92" min="1" max="1"/>
@@ -27412,14 +27320,6 @@
           <t>DEGISIKLIK KAYDI — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
@@ -27503,14 +27403,6 @@
           <t>LISTELER — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
@@ -27603,13 +27495,6 @@
           <t>AYARLAR — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
@@ -29097,14 +28982,6 @@
           <t>KILAVUZ — ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
@@ -29232,7 +29109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="66" min="1" max="1"/>
@@ -29696,7 +29573,7 @@
         </is>
       </c>
       <c r="E17" s="217">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -29719,7 +29596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="66" min="1" max="1"/>
@@ -29886,7 +29763,7 @@
       <c r="C11" s="159" t="n"/>
       <c r="D11" s="159" t="n"/>
       <c r="E11" s="264">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="159" t="n"/>
@@ -30043,7 +29920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="66" min="1" max="1"/>
@@ -30064,14 +29941,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
@@ -30546,7 +30415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="66" min="1" max="1"/>
@@ -30567,14 +30436,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
@@ -31301,7 +31162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" style="66" min="1" max="1"/>
@@ -31322,14 +31183,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
@@ -31987,7 +31840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" style="66" min="1" max="1"/>
@@ -32008,14 +31861,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
@@ -32545,7 +32390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" style="66" min="1" max="1"/>
@@ -32566,14 +32411,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="266" t="n"/>
-      <c r="C1" s="266" t="n"/>
-      <c r="D1" s="266" t="n"/>
-      <c r="E1" s="266" t="n"/>
-      <c r="F1" s="266" t="n"/>
-      <c r="G1" s="266" t="n"/>
-      <c r="H1" s="266" t="n"/>
-      <c r="I1" s="266" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">

--- a/EXCELARSIV_PRODUCTS/asgari-ucret-zam-etkisi-fiyat-ayarlama-cetveli/AsgariUcretZamEtkisiFiyatAyarlamaCetveli.xlsx
+++ b/EXCELARSIV_PRODUCTS/asgari-ucret-zam-etkisi-fiyat-ayarlama-cetveli/AsgariUcretZamEtkisiFiyatAyarlamaCetveli.xlsx
@@ -144,7 +144,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="99">
+  <fonts count="135">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -759,8 +759,220 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="41">
     <fill>
       <patternFill/>
     </fill>
@@ -964,8 +1176,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="34">
+  <borders count="70">
     <border>
       <left/>
       <right/>
@@ -1327,6 +1563,348 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1338,7 +1916,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="285">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2059,6 +2637,235 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="20" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="20" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="20" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="20" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="102" fillId="20" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="104" fillId="20" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="102" fillId="20" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="20" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="20" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="20" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="20" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="20" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="9" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="9" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="52" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="77" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="110" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="52" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="77" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="116" fillId="9" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="117" fillId="9" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="118" fillId="9" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="20" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="19" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="20" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="20" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="20" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="19" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="121" fillId="20" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="19" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="20" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="20" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="128" fillId="14" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="13" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="129" fillId="20" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="130" fillId="20" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="20" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="134" fillId="20" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="119" fillId="20" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="131" fillId="20" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="131" fillId="20" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="20" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="14" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="13" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="20" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="20" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="20" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3540,7 +4347,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
       <c r="A3" s="232" t="inlineStr">
         <is>
@@ -3805,7 +4611,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1" s="66">
       <c r="A26" s="235" t="inlineStr">
         <is>
@@ -3938,7 +4743,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
       <c r="A3" s="284" t="inlineStr">
         <is>
@@ -3975,7 +4779,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="66">
       <c r="A10" s="97" t="inlineStr">
         <is>
@@ -3986,7 +4789,6 @@
     <row r="11" ht="15" customHeight="1" s="66"/>
     <row r="12" ht="15" customHeight="1" s="66"/>
     <row r="13" ht="15" customHeight="1" s="66"/>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="66">
       <c r="A15" s="98" t="inlineStr">
         <is>
@@ -4047,7 +4849,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
       <c r="A3" s="284" t="inlineStr">
         <is>
@@ -4104,7 +4905,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="66">
       <c r="A12" s="102" t="inlineStr">
         <is>
@@ -4147,7 +4947,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="19.5" customHeight="1" s="66">
       <c r="A19" s="103" t="inlineStr">
         <is>
@@ -4210,7 +5009,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
       <c r="A3" s="284" t="inlineStr">
         <is>
@@ -11896,7 +12694,6 @@
       <c r="D1004" s="113" t="n"/>
       <c r="E1004" s="113" t="n"/>
     </row>
-    <row r="1005"/>
     <row r="1006" ht="19.5" customHeight="1" s="66">
       <c r="A1006" s="103" t="inlineStr">
         <is>
@@ -11985,7 +12782,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
       <c r="A3" s="284" t="inlineStr">
         <is>
@@ -24341,7 +25137,6 @@
       <c r="C2004" s="113" t="n"/>
       <c r="D2004" s="113" t="n"/>
     </row>
-    <row r="2005"/>
     <row r="2006" ht="19.5" customHeight="1" s="66">
       <c r="A2006" s="103" t="inlineStr">
         <is>
@@ -24418,7 +25213,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
       <c r="A3" s="284" t="inlineStr">
         <is>
@@ -24433,7 +25227,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="66">
       <c r="A6" s="115" t="inlineStr">
         <is>
@@ -24617,7 +25410,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="66">
       <c r="A24" s="105" t="inlineStr">
         <is>
@@ -25124,7 +25916,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
       <c r="A3" s="284" t="inlineStr">
         <is>
@@ -25132,7 +25923,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="66">
       <c r="A5" s="116" t="inlineStr">
         <is>
@@ -25221,8 +26011,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="66">
       <c r="A15" s="115" t="inlineStr">
         <is>
@@ -25329,7 +26117,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="19.5" customHeight="1" s="66">
       <c r="A26" s="103" t="inlineStr">
         <is>
@@ -25408,7 +26195,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="66">
       <c r="A3" s="105" t="inlineStr">
         <is>
@@ -25416,7 +26202,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="66">
       <c r="A5" s="115" t="inlineStr">
         <is>
@@ -25468,7 +26253,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="18.75" customHeight="1" s="66">
       <c r="A11" s="105" t="inlineStr">
         <is>
@@ -25491,7 +26275,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="66">
       <c r="A14" s="115" t="inlineStr">
         <is>
@@ -25523,8 +26306,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21" ht="19.5" customHeight="1" s="66">
       <c r="A21" s="103" t="inlineStr">
         <is>
@@ -25604,7 +26385,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
       <c r="A3" s="284" t="inlineStr">
         <is>
@@ -25612,8 +26392,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1" s="66">
       <c r="A6" s="107" t="inlineStr">
         <is>
@@ -25731,7 +26509,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="66">
       <c r="A13" s="115" t="inlineStr">
         <is>
@@ -25777,7 +26554,6 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="66">
       <c r="A17" s="122" t="inlineStr">
         <is>
@@ -25789,7 +26565,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="19.5" customHeight="1" s="66">
       <c r="A19" s="103" t="inlineStr">
         <is>
@@ -25895,7 +26670,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="15" customHeight="1" s="66">
       <c r="A8" s="115" t="inlineStr">
         <is>
@@ -25991,7 +26765,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="66">
       <c r="A18" s="142">
         <f>KararGerekce</f>
@@ -26027,7 +26800,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25" ht="15" customHeight="1" s="66">
       <c r="A25" s="115" t="inlineStr">
         <is>
@@ -26056,7 +26828,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="66">
       <c r="A30" s="115" t="inlineStr">
         <is>
@@ -26085,8 +26856,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36" ht="15" customHeight="1" s="66">
       <c r="A36" s="99" t="inlineStr">
         <is>
@@ -26185,7 +26954,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
       <c r="A3" s="284" t="inlineStr">
         <is>
@@ -26193,7 +26961,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="66">
       <c r="A5" s="107" t="inlineStr">
         <is>
@@ -26359,8 +27126,6 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="66">
       <c r="A14" s="105" t="inlineStr">
         <is>
@@ -26368,7 +27133,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="30" customHeight="1" s="66">
       <c r="A16" s="107" t="inlineStr">
         <is>
@@ -26456,7 +27220,6 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="19.5" customHeight="1" s="66">
       <c r="A22" s="103" t="inlineStr">
         <is>
@@ -26487,554 +27250,585 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="66" min="1" max="1"/>
-    <col width="83.5" customWidth="1" style="66" min="2" max="2"/>
-    <col width="15" customWidth="1" style="66" min="3" max="3"/>
-    <col width="15.5" customWidth="1" style="66" min="4" max="4"/>
-    <col width="36.5" customWidth="1" style="66" min="5" max="5"/>
-    <col width="18" customWidth="1" style="66" min="6" max="6"/>
-    <col width="11.5" customWidth="1" style="66" min="7" max="7"/>
-    <col width="75.5" customWidth="1" style="66" min="8" max="8"/>
-    <col width="15" customWidth="1" style="66" min="9" max="9"/>
-    <col width="15.5" customWidth="1" style="66" min="10" max="10"/>
-    <col width="81.5" customWidth="1" style="66" min="11" max="11"/>
-    <col width="18" customWidth="1" style="66" min="12" max="12"/>
-    <col width="18" customWidth="1" style="66" min="13" max="13"/>
-    <col width="13" customWidth="1" style="66" min="14" max="14"/>
+    <col width="12" customWidth="1" style="66" min="1" max="1"/>
+    <col width="17" customWidth="1" style="66" min="2" max="2"/>
+    <col width="12" customWidth="1" style="66" min="3" max="3"/>
+    <col width="11" customWidth="1" style="66" min="4" max="4"/>
+    <col width="17" customWidth="1" style="66" min="5" max="5"/>
+    <col width="12" customWidth="1" style="66" min="6" max="6"/>
+    <col width="11" customWidth="1" style="66" min="7" max="7"/>
+    <col width="17" customWidth="1" style="66" min="8" max="8"/>
+    <col width="13" customWidth="1" style="66" min="9" max="9"/>
+    <col width="11" customWidth="1" style="66" min="10" max="10"/>
+    <col width="17" customWidth="1" style="66" min="11" max="11"/>
+    <col width="14" customWidth="1" style="66" min="12" max="12"/>
+    <col width="12" customWidth="1" style="66" min="13" max="13"/>
+    <col width="6" customWidth="1" style="66" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="76" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="66">
+      <c r="A1" s="285" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="154" t="inlineStr">
+    <row r="2" ht="28" customHeight="1" s="66">
+      <c r="B2" s="286" t="inlineStr">
         <is>
           <t>ASGARI ÜCRET ZAM ETKISI &amp; FIYAT AYARLAMA CETVELI</t>
         </is>
       </c>
-      <c r="L2" s="155" t="inlineStr">
+      <c r="L2" s="287" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="156" t="inlineStr">
+      <c r="M2" s="288" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="157" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="66">
+      <c r="B3" s="289" t="inlineStr">
         <is>
           <t>Hedef Kullanıcı: KOBİ sahipleri, işletme yöneticileri, mali müşavirler, fiyatlandırma ve İK bütçesi yapan profesyoneller · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="158" t="inlineStr">
+    <row r="4" ht="10" customHeight="1" s="66"/>
+    <row r="5" ht="20" customHeight="1" s="66">
+      <c r="B5" s="290" t="inlineStr">
         <is>
           <t>TOPLAM İŞLEM HACMİ</t>
         </is>
       </c>
-      <c r="C5" s="159" t="n"/>
-      <c r="D5" s="160" t="inlineStr">
+      <c r="C5" s="291" t="n"/>
+      <c r="D5" s="292" t="inlineStr">
         <is>
           <t>KONSOLİDE</t>
         </is>
       </c>
-      <c r="E5" s="161" t="inlineStr">
+      <c r="E5" s="293" t="inlineStr">
         <is>
           <t>OPERASYONEL MALİYET</t>
         </is>
       </c>
-      <c r="F5" s="159" t="n"/>
-      <c r="G5" s="162" t="inlineStr">
+      <c r="F5" s="291" t="n"/>
+      <c r="G5" s="294" t="inlineStr">
         <is>
           <t>KONTROL</t>
         </is>
       </c>
-      <c r="H5" s="158" t="inlineStr">
+      <c r="H5" s="295" t="inlineStr">
         <is>
           <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
-      <c r="I5" s="159" t="n"/>
-      <c r="J5" s="163" t="inlineStr">
+      <c r="I5" s="291" t="n"/>
+      <c r="J5" s="296" t="inlineStr">
         <is>
           <t>GÜVENLİ</t>
         </is>
       </c>
-      <c r="K5" s="164" t="inlineStr">
+      <c r="K5" s="297" t="inlineStr">
         <is>
           <t>SİSTEM GÜVEN SKORU</t>
         </is>
       </c>
-      <c r="L5" s="159" t="n"/>
-      <c r="M5" s="160" t="inlineStr">
+      <c r="L5" s="291" t="n"/>
+      <c r="M5" s="298" t="inlineStr">
         <is>
           <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="165" t="n"/>
-      <c r="C6" s="159" t="n"/>
-      <c r="D6" s="159" t="n"/>
-      <c r="E6" s="166" t="n"/>
-      <c r="F6" s="159" t="n"/>
-      <c r="G6" s="159" t="n"/>
-      <c r="H6" s="165" t="n"/>
-      <c r="I6" s="159" t="n"/>
-      <c r="J6" s="159" t="n"/>
-      <c r="K6" s="167" t="n"/>
-      <c r="L6" s="159" t="n"/>
-      <c r="M6" s="159" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="255">
+    <row r="6" ht="6" customHeight="1" s="66">
+      <c r="B6" s="299" t="n"/>
+      <c r="C6" s="300" t="n"/>
+      <c r="D6" s="301" t="n"/>
+      <c r="E6" s="302" t="n"/>
+      <c r="F6" s="300" t="n"/>
+      <c r="G6" s="301" t="n"/>
+      <c r="H6" s="303" t="n"/>
+      <c r="I6" s="300" t="n"/>
+      <c r="J6" s="301" t="n"/>
+      <c r="K6" s="304" t="n"/>
+      <c r="L6" s="300" t="n"/>
+      <c r="M6" s="301" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1" s="66">
+      <c r="B7" s="305">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="159" t="n"/>
-      <c r="D7" s="159" t="n"/>
-      <c r="E7" s="256">
+      <c r="C7" s="300" t="n"/>
+      <c r="D7" s="301" t="n"/>
+      <c r="E7" s="306">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="159" t="n"/>
-      <c r="G7" s="159" t="n"/>
-      <c r="H7" s="255">
+      <c r="F7" s="300" t="n"/>
+      <c r="G7" s="301" t="n"/>
+      <c r="H7" s="307">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="159" t="n"/>
-      <c r="J7" s="159" t="n"/>
-      <c r="K7" s="170">
+      <c r="I7" s="300" t="n"/>
+      <c r="J7" s="301" t="n"/>
+      <c r="K7" s="308">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="159" t="n"/>
-      <c r="M7" s="159" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="165" t="n"/>
-      <c r="C8" s="159" t="n"/>
-      <c r="D8" s="159" t="n"/>
-      <c r="E8" s="166" t="n"/>
-      <c r="F8" s="159" t="n"/>
-      <c r="G8" s="159" t="n"/>
-      <c r="H8" s="165" t="n"/>
-      <c r="I8" s="159" t="n"/>
-      <c r="J8" s="159" t="n"/>
-      <c r="K8" s="167" t="n"/>
-      <c r="L8" s="159" t="n"/>
-      <c r="M8" s="159" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="171" t="inlineStr">
+      <c r="L7" s="300" t="n"/>
+      <c r="M7" s="301" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1" s="66">
+      <c r="B8" s="299" t="n"/>
+      <c r="C8" s="300" t="n"/>
+      <c r="D8" s="301" t="n"/>
+      <c r="E8" s="302" t="n"/>
+      <c r="F8" s="300" t="n"/>
+      <c r="G8" s="301" t="n"/>
+      <c r="H8" s="303" t="n"/>
+      <c r="I8" s="300" t="n"/>
+      <c r="J8" s="301" t="n"/>
+      <c r="K8" s="304" t="n"/>
+      <c r="L8" s="300" t="n"/>
+      <c r="M8" s="301" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="66">
+      <c r="B9" s="309" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="159" t="n"/>
-      <c r="D9" s="159" t="n"/>
-      <c r="E9" s="172" t="inlineStr">
+      <c r="C9" s="310" t="n"/>
+      <c r="D9" s="311" t="n"/>
+      <c r="E9" s="312" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="159" t="n"/>
-      <c r="G9" s="159" t="n"/>
-      <c r="H9" s="171" t="inlineStr">
+      <c r="F9" s="310" t="n"/>
+      <c r="G9" s="311" t="n"/>
+      <c r="H9" s="313" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="159" t="n"/>
-      <c r="J9" s="159" t="n"/>
-      <c r="K9" s="173" t="inlineStr">
+      <c r="I9" s="310" t="n"/>
+      <c r="J9" s="311" t="n"/>
+      <c r="K9" s="314" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="159" t="n"/>
-      <c r="M9" s="159" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="90" t="inlineStr">
+      <c r="L9" s="310" t="n"/>
+      <c r="M9" s="311" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1" s="66"/>
+    <row r="11" ht="24" customHeight="1" s="66">
+      <c r="B11" s="315" t="inlineStr">
         <is>
           <t>ASGARI ÜCRET ZAM ETKISI &amp; FIYAT AYARLAMA CETVELI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="174" t="inlineStr">
+      <c r="F11" s="316" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="90" t="inlineStr">
+      <c r="H11" s="315" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="89" t="inlineStr">
+    <row r="12" ht="18" customHeight="1" s="66">
+      <c r="B12" s="157" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="89" t="inlineStr">
+      <c r="H12" s="157" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="175" t="inlineStr">
+    <row r="13" ht="8" customHeight="1" s="66"/>
+    <row r="14" ht="24" customHeight="1" s="66">
+      <c r="B14" s="317" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="175" t="inlineStr">
+      <c r="C14" s="317" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="175" t="inlineStr">
+      <c r="D14" s="317" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="175" t="inlineStr">
+      <c r="E14" s="317" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="176" t="inlineStr">
+      <c r="H14" s="318" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="176" t="inlineStr">
+      <c r="I14" s="319" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="176" t="inlineStr">
+      <c r="J14" s="319" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="176" t="inlineStr">
+      <c r="K14" s="319" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="176" t="inlineStr">
+      <c r="L14" s="319" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="89" t="inlineStr">
+      <c r="M14" s="319" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="66">
+      <c r="B15" s="320" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="89" t="n">
+      <c r="C15" s="320" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="89" t="n">
+      <c r="D15" s="320" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="89" t="n">
+      <c r="E15" s="320" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="177" t="inlineStr">
+      <c r="H15" s="321" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="257">
+      <c r="I15" s="322">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="258">
+      <c r="J15" s="323">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="179" t="inlineStr">
+      <c r="K15" s="324" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="163" t="inlineStr">
+      <c r="L15" s="325" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="89" t="inlineStr">
+      <c r="M15" s="326" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="66">
+      <c r="B16" s="327" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="89" t="n">
+      <c r="C16" s="327" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="89" t="n">
+      <c r="D16" s="327" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="89" t="n">
+      <c r="E16" s="327" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="177" t="inlineStr">
+      <c r="H16" s="328" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="257">
+      <c r="I16" s="329">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="258">
+      <c r="J16" s="330">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="179" t="inlineStr">
+      <c r="K16" s="331" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="160" t="inlineStr">
+      <c r="L16" s="332" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="89" t="inlineStr">
+      <c r="M16" s="333" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" s="66">
+      <c r="B17" s="320" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="89" t="n">
+      <c r="C17" s="320" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="89" t="n">
+      <c r="D17" s="320" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="89" t="n">
+      <c r="E17" s="320" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="177" t="inlineStr">
+      <c r="H17" s="321" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="257">
+      <c r="I17" s="322">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="258">
+      <c r="J17" s="323">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="179" t="inlineStr">
+      <c r="K17" s="324" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="180" t="inlineStr">
+      <c r="L17" s="334" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="89" t="inlineStr">
+      <c r="M17" s="326" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="66">
+      <c r="B18" s="327" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="89" t="n">
+      <c r="C18" s="327" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="89" t="n">
+      <c r="D18" s="327" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="89" t="n">
+      <c r="E18" s="327" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="177" t="inlineStr">
+      <c r="H18" s="328" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="257">
+      <c r="I18" s="329">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="258">
+      <c r="J18" s="330">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="179" t="inlineStr">
+      <c r="K18" s="331" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="163" t="inlineStr">
+      <c r="L18" s="335" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="89" t="inlineStr">
+      <c r="M18" s="333" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1" s="66">
+      <c r="B19" s="320" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="89" t="n">
+      <c r="C19" s="320" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="89" t="n">
+      <c r="D19" s="320" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="89" t="n">
+      <c r="E19" s="320" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="181" t="inlineStr">
+      <c r="H19" s="336" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="259">
+      <c r="I19" s="337">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="260">
+      <c r="J19" s="338">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="184" t="inlineStr"/>
-      <c r="L19" s="185" t="inlineStr">
+      <c r="K19" s="339" t="inlineStr"/>
+      <c r="L19" s="340" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="89" t="inlineStr">
+      <c r="M19" s="340" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="66">
+      <c r="B20" s="327" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="89" t="n">
+      <c r="C20" s="327" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="89" t="n">
+      <c r="D20" s="327" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="89" t="n">
+      <c r="E20" s="327" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="186" t="inlineStr">
+    <row r="21" ht="14" customHeight="1" s="66"/>
+    <row r="22" ht="24" customHeight="1" s="66">
+      <c r="B22" s="341" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="186" t="inlineStr">
+      <c r="C22" s="291" t="n"/>
+      <c r="D22" s="291" t="n"/>
+      <c r="E22" s="342" t="n"/>
+      <c r="F22" s="341" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="187" t="inlineStr">
+      <c r="G22" s="291" t="n"/>
+      <c r="H22" s="291" t="n"/>
+      <c r="I22" s="342" t="n"/>
+      <c r="K22" s="343" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="188" t="n"/>
-      <c r="M22" s="188" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="74" t="inlineStr">
+      <c r="L22" s="344" t="n"/>
+      <c r="M22" s="345" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="66">
+      <c r="B23" s="346" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="89" t="inlineStr">
+      <c r="C23" s="300" t="n"/>
+      <c r="D23" s="300" t="n"/>
+      <c r="E23" s="301" t="n"/>
+      <c r="F23" s="347" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="189" t="inlineStr">
+      <c r="G23" s="300" t="n"/>
+      <c r="H23" s="300" t="n"/>
+      <c r="I23" s="348" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="190" t="inlineStr">
-        <is>
-          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
-        </is>
-      </c>
-      <c r="L23" s="188" t="n"/>
-      <c r="M23" s="188" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="75" t="inlineStr">
+      <c r="K23" s="349" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="350" t="n"/>
+      <c r="M23" s="351" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="66">
+      <c r="B24" s="352" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="89" t="inlineStr">
+      <c r="C24" s="300" t="n"/>
+      <c r="D24" s="300" t="n"/>
+      <c r="E24" s="301" t="n"/>
+      <c r="F24" s="347" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="189" t="inlineStr">
+      <c r="G24" s="300" t="n"/>
+      <c r="H24" s="300" t="n"/>
+      <c r="I24" s="348" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="191" t="inlineStr">
-        <is>
-          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="192" t="inlineStr">
+      <c r="K24" s="353" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="66">
+      <c r="B25" s="354" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="74" t="inlineStr">
+      <c r="C25" s="300" t="n"/>
+      <c r="D25" s="300" t="n"/>
+      <c r="E25" s="301" t="n"/>
+      <c r="F25" s="325" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="193" t="inlineStr">
+      <c r="G25" s="355" t="n"/>
+      <c r="H25" s="355" t="n"/>
+      <c r="I25" s="355" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="66">
+      <c r="B26" s="356" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="194" t="inlineStr">
+      <c r="C26" s="300" t="n"/>
+      <c r="D26" s="300" t="n"/>
+      <c r="E26" s="301" t="n"/>
+      <c r="F26" s="357" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
@@ -27042,23 +27836,29 @@
       <c r="G26" s="267" t="n"/>
       <c r="H26" s="267" t="n"/>
       <c r="I26" s="268" t="n"/>
-      <c r="K26" s="195" t="inlineStr">
-        <is>
-          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="K26" s="358" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1" s="66">
+      <c r="B27" s="359" t="n"/>
+      <c r="C27" s="310" t="n"/>
+      <c r="D27" s="310" t="n"/>
+      <c r="E27" s="311" t="n"/>
       <c r="F27" s="269" t="n"/>
       <c r="G27" s="270" t="n"/>
       <c r="H27" s="270" t="n"/>
       <c r="I27" s="271" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27092,7 +27892,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="66">
       <c r="A3" s="92" t="inlineStr">
         <is>
@@ -27270,7 +28069,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="66">
       <c r="A9" s="92" t="inlineStr">
         <is>
@@ -27321,7 +28119,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
       <c r="A3" s="284" t="inlineStr">
         <is>
@@ -27329,7 +28126,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="66">
       <c r="A5" s="107" t="inlineStr">
         <is>
@@ -27404,7 +28200,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
       <c r="A3" s="284" t="inlineStr">
         <is>
@@ -27419,7 +28214,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="66">
       <c r="A6" s="145" t="inlineStr">
         <is>
@@ -27441,8 +28235,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="19.5" customHeight="1" s="66">
       <c r="A11" s="103" t="inlineStr">
         <is>
@@ -27496,7 +28288,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
       <c r="A3" s="284" t="inlineStr">
         <is>
@@ -28796,7 +29587,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38" ht="19.5" customHeight="1" s="66">
       <c r="A38" s="103" t="inlineStr">
         <is>
@@ -28804,7 +29594,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="15" customHeight="1" s="66">
       <c r="J40" s="92" t="inlineStr">
         <is>
@@ -28983,7 +29772,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="66">
       <c r="A3" s="284" t="inlineStr">
         <is>
@@ -28991,7 +29779,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="66">
       <c r="A5" s="101" t="inlineStr">
         <is>
@@ -29069,8 +29856,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
     <row r="18" ht="19.5" customHeight="1" s="66">
       <c r="A18" s="103" t="inlineStr">
         <is>
@@ -29131,7 +29916,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="196" t="inlineStr">
         <is>
@@ -29152,7 +29936,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="199" t="inlineStr">
         <is>
@@ -29565,7 +30348,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="216" t="inlineStr">
         <is>
@@ -29596,54 +30378,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="66" min="1" max="1"/>
+    <col width="12" customWidth="1" style="66" min="1" max="1"/>
     <col width="24" customWidth="1" style="66" min="2" max="2"/>
-    <col width="15" customWidth="1" style="66" min="3" max="3"/>
-    <col width="15" customWidth="1" style="66" min="4" max="4"/>
-    <col width="22" customWidth="1" style="66" min="5" max="5"/>
-    <col width="6" customWidth="1" style="66" min="6" max="6"/>
+    <col width="14" customWidth="1" style="66" min="3" max="3"/>
+    <col width="14" customWidth="1" style="66" min="4" max="4"/>
+    <col width="16" customWidth="1" style="66" min="5" max="5"/>
+    <col width="14" customWidth="1" style="66" min="6" max="6"/>
     <col width="6" customWidth="1" style="66" min="7" max="7"/>
     <col width="24" customWidth="1" style="66" min="8" max="8"/>
-    <col width="15" customWidth="1" style="66" min="9" max="9"/>
-    <col width="15" customWidth="1" style="66" min="10" max="10"/>
-    <col width="22" customWidth="1" style="66" min="11" max="11"/>
-    <col width="6" customWidth="1" style="66" min="12" max="12"/>
+    <col width="14" customWidth="1" style="66" min="9" max="9"/>
+    <col width="14" customWidth="1" style="66" min="10" max="10"/>
+    <col width="16" customWidth="1" style="66" min="11" max="11"/>
+    <col width="14" customWidth="1" style="66" min="12" max="12"/>
+    <col width="6" customWidth="1" style="66" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="76" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="66">
+      <c r="A1" s="285" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1" s="66">
       <c r="B2" s="218" t="inlineStr">
         <is>
           <t>ASGARI ÜCRET ZAM ETKISI &amp; FIYAT AYARLAMA CETVELI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="219" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="66">
+      <c r="B3" s="360" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · KOBİ sahipleri, işletme yöneticileri, mali müşavirler, fiyatlandırma ve İK bütçesi yapan profesyoneller</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="220" t="inlineStr">
+    <row r="4" ht="20" customHeight="1" s="66">
+      <c r="B4" s="361" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="221" t="inlineStr">
+    <row r="5" ht="12" customHeight="1" s="66"/>
+    <row r="6" ht="26" customHeight="1" s="66">
+      <c r="B6" s="362" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
@@ -29652,7 +30435,7 @@
       <c r="D6" s="272" t="n"/>
       <c r="E6" s="272" t="n"/>
       <c r="F6" s="273" t="n"/>
-      <c r="H6" s="222" t="inlineStr">
+      <c r="H6" s="363" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
@@ -29662,151 +30445,151 @@
       <c r="K6" s="272" t="n"/>
       <c r="L6" s="273" t="n"/>
     </row>
-    <row r="7">
-      <c r="B7" s="159" t="n"/>
-      <c r="C7" s="159" t="n"/>
-      <c r="D7" s="159" t="n"/>
-      <c r="E7" s="159" t="n"/>
-      <c r="F7" s="159" t="n"/>
-      <c r="H7" s="159" t="n"/>
-      <c r="I7" s="159" t="n"/>
-      <c r="J7" s="159" t="n"/>
-      <c r="K7" s="159" t="n"/>
-      <c r="L7" s="159" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="223" t="inlineStr">
+    <row r="7" ht="22" customHeight="1" s="66">
+      <c r="B7" s="364" t="n"/>
+      <c r="C7" s="300" t="n"/>
+      <c r="D7" s="300" t="n"/>
+      <c r="E7" s="300" t="n"/>
+      <c r="F7" s="365" t="n"/>
+      <c r="H7" s="366" t="n"/>
+      <c r="I7" s="300" t="n"/>
+      <c r="J7" s="300" t="n"/>
+      <c r="K7" s="300" t="n"/>
+      <c r="L7" s="367" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="66">
+      <c r="B8" s="368" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="159" t="n"/>
-      <c r="D8" s="159" t="n"/>
-      <c r="E8" s="224" t="inlineStr">
+      <c r="C8" s="300" t="n"/>
+      <c r="D8" s="300" t="n"/>
+      <c r="E8" s="369" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="159" t="n"/>
-      <c r="H8" s="223" t="inlineStr">
+      <c r="F8" s="365" t="n"/>
+      <c r="H8" s="370" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="159" t="n"/>
-      <c r="J8" s="159" t="n"/>
-      <c r="K8" s="225" t="inlineStr">
+      <c r="I8" s="300" t="n"/>
+      <c r="J8" s="300" t="n"/>
+      <c r="K8" s="371" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="159" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="223" t="inlineStr">
+      <c r="L8" s="367" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="66">
+      <c r="B9" s="368" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="159" t="n"/>
-      <c r="D9" s="159" t="n"/>
-      <c r="E9" s="262">
+      <c r="C9" s="300" t="n"/>
+      <c r="D9" s="300" t="n"/>
+      <c r="E9" s="372">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="159" t="n"/>
-      <c r="H9" s="223" t="inlineStr">
+      <c r="F9" s="365" t="n"/>
+      <c r="H9" s="370" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="159" t="n"/>
-      <c r="J9" s="159" t="n"/>
-      <c r="K9" s="262">
+      <c r="I9" s="300" t="n"/>
+      <c r="J9" s="300" t="n"/>
+      <c r="K9" s="372">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="159" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="223" t="inlineStr">
+      <c r="L9" s="367" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" s="66">
+      <c r="B10" s="368" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="159" t="n"/>
-      <c r="D10" s="159" t="n"/>
-      <c r="E10" s="263">
+      <c r="C10" s="300" t="n"/>
+      <c r="D10" s="300" t="n"/>
+      <c r="E10" s="373">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="159" t="n"/>
-      <c r="H10" s="223" t="inlineStr">
+      <c r="F10" s="365" t="n"/>
+      <c r="H10" s="370" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="159" t="n"/>
-      <c r="J10" s="159" t="n"/>
-      <c r="K10" s="263">
+      <c r="I10" s="300" t="n"/>
+      <c r="J10" s="300" t="n"/>
+      <c r="K10" s="373">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="159" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="223" t="inlineStr">
+      <c r="L10" s="367" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" s="66">
+      <c r="B11" s="368" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="159" t="n"/>
-      <c r="D11" s="159" t="n"/>
-      <c r="E11" s="264">
+      <c r="C11" s="300" t="n"/>
+      <c r="D11" s="300" t="n"/>
+      <c r="E11" s="374">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="159" t="n"/>
-      <c r="H11" s="223" t="inlineStr">
+      <c r="F11" s="365" t="n"/>
+      <c r="H11" s="370" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="159" t="n"/>
-      <c r="J11" s="159" t="n"/>
-      <c r="K11" s="227" t="inlineStr">
+      <c r="I11" s="300" t="n"/>
+      <c r="J11" s="300" t="n"/>
+      <c r="K11" s="375" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="159" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="159" t="n"/>
-      <c r="C12" s="159" t="n"/>
-      <c r="D12" s="159" t="n"/>
-      <c r="E12" s="159" t="n"/>
-      <c r="F12" s="159" t="n"/>
-      <c r="H12" s="159" t="n"/>
-      <c r="I12" s="159" t="n"/>
-      <c r="J12" s="159" t="n"/>
-      <c r="K12" s="159" t="n"/>
-      <c r="L12" s="159" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="159" t="n"/>
-      <c r="C13" s="159" t="n"/>
-      <c r="D13" s="159" t="n"/>
-      <c r="E13" s="159" t="n"/>
-      <c r="F13" s="159" t="n"/>
-      <c r="H13" s="159" t="n"/>
-      <c r="I13" s="159" t="n"/>
-      <c r="J13" s="159" t="n"/>
-      <c r="K13" s="159" t="n"/>
-      <c r="L13" s="159" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="228" t="inlineStr">
+      <c r="L11" s="367" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="66">
+      <c r="B12" s="364" t="n"/>
+      <c r="C12" s="300" t="n"/>
+      <c r="D12" s="300" t="n"/>
+      <c r="E12" s="300" t="n"/>
+      <c r="F12" s="365" t="n"/>
+      <c r="H12" s="366" t="n"/>
+      <c r="I12" s="300" t="n"/>
+      <c r="J12" s="300" t="n"/>
+      <c r="K12" s="300" t="n"/>
+      <c r="L12" s="367" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="66">
+      <c r="B13" s="364" t="n"/>
+      <c r="C13" s="300" t="n"/>
+      <c r="D13" s="300" t="n"/>
+      <c r="E13" s="300" t="n"/>
+      <c r="F13" s="365" t="n"/>
+      <c r="H13" s="366" t="n"/>
+      <c r="I13" s="300" t="n"/>
+      <c r="J13" s="300" t="n"/>
+      <c r="K13" s="300" t="n"/>
+      <c r="L13" s="367" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" s="66">
+      <c r="B14" s="376" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
@@ -29815,7 +30598,7 @@
       <c r="D14" s="274" t="n"/>
       <c r="E14" s="274" t="n"/>
       <c r="F14" s="275" t="n"/>
-      <c r="H14" s="229" t="inlineStr">
+      <c r="H14" s="377" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
@@ -29825,7 +30608,7 @@
       <c r="K14" s="276" t="n"/>
       <c r="L14" s="277" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1" s="66">
       <c r="B15" s="278" t="n"/>
       <c r="C15" s="279" t="n"/>
       <c r="D15" s="279" t="n"/>
@@ -29837,70 +30620,185 @@
       <c r="K15" s="282" t="n"/>
       <c r="L15" s="283" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="77" t="inlineStr">
+    <row r="16" ht="10" customHeight="1" s="66"/>
+    <row r="17" ht="26" customHeight="1" s="66">
+      <c r="B17" s="378" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="186" t="inlineStr">
+      <c r="C17" s="291" t="n"/>
+      <c r="D17" s="291" t="n"/>
+      <c r="E17" s="291" t="n"/>
+      <c r="F17" s="291" t="n"/>
+      <c r="G17" s="291" t="n"/>
+      <c r="H17" s="291" t="n"/>
+      <c r="I17" s="291" t="n"/>
+      <c r="J17" s="291" t="n"/>
+      <c r="K17" s="291" t="n"/>
+      <c r="L17" s="342" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="66">
+      <c r="B18" s="379" t="n"/>
+      <c r="C18" s="300" t="n"/>
+      <c r="D18" s="300" t="n"/>
+      <c r="E18" s="300" t="n"/>
+      <c r="F18" s="300" t="n"/>
+      <c r="G18" s="300" t="n"/>
+      <c r="H18" s="300" t="n"/>
+      <c r="I18" s="300" t="n"/>
+      <c r="J18" s="300" t="n"/>
+      <c r="K18" s="300" t="n"/>
+      <c r="L18" s="301" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="66">
+      <c r="B19" s="380" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="230" t="inlineStr">
+      <c r="C19" s="300" t="n"/>
+      <c r="D19" s="300" t="n"/>
+      <c r="E19" s="300" t="n"/>
+      <c r="F19" s="300" t="n"/>
+      <c r="G19" s="300" t="n"/>
+      <c r="H19" s="300" t="n"/>
+      <c r="I19" s="300" t="n"/>
+      <c r="J19" s="300" t="n"/>
+      <c r="K19" s="300" t="n"/>
+      <c r="L19" s="301" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="66">
+      <c r="B20" s="381" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="186" t="inlineStr">
+      <c r="C20" s="300" t="n"/>
+      <c r="D20" s="300" t="n"/>
+      <c r="E20" s="300" t="n"/>
+      <c r="F20" s="300" t="n"/>
+      <c r="G20" s="300" t="n"/>
+      <c r="H20" s="300" t="n"/>
+      <c r="I20" s="300" t="n"/>
+      <c r="J20" s="300" t="n"/>
+      <c r="K20" s="300" t="n"/>
+      <c r="L20" s="301" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1" s="66">
+      <c r="B21" s="380" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="230" t="inlineStr">
+      <c r="C21" s="300" t="n"/>
+      <c r="D21" s="300" t="n"/>
+      <c r="E21" s="300" t="n"/>
+      <c r="F21" s="300" t="n"/>
+      <c r="G21" s="300" t="n"/>
+      <c r="H21" s="300" t="n"/>
+      <c r="I21" s="300" t="n"/>
+      <c r="J21" s="300" t="n"/>
+      <c r="K21" s="300" t="n"/>
+      <c r="L21" s="301" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="66">
+      <c r="B22" s="381" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="186" t="inlineStr">
+      <c r="C22" s="300" t="n"/>
+      <c r="D22" s="300" t="n"/>
+      <c r="E22" s="300" t="n"/>
+      <c r="F22" s="300" t="n"/>
+      <c r="G22" s="300" t="n"/>
+      <c r="H22" s="300" t="n"/>
+      <c r="I22" s="300" t="n"/>
+      <c r="J22" s="300" t="n"/>
+      <c r="K22" s="300" t="n"/>
+      <c r="L22" s="301" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="66">
+      <c r="B23" s="380" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="230" t="inlineStr">
+      <c r="C23" s="300" t="n"/>
+      <c r="D23" s="300" t="n"/>
+      <c r="E23" s="300" t="n"/>
+      <c r="F23" s="300" t="n"/>
+      <c r="G23" s="300" t="n"/>
+      <c r="H23" s="300" t="n"/>
+      <c r="I23" s="300" t="n"/>
+      <c r="J23" s="300" t="n"/>
+      <c r="K23" s="300" t="n"/>
+      <c r="L23" s="301" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="66">
+      <c r="B24" s="381" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="186" t="inlineStr">
+      <c r="C24" s="300" t="n"/>
+      <c r="D24" s="300" t="n"/>
+      <c r="E24" s="300" t="n"/>
+      <c r="F24" s="300" t="n"/>
+      <c r="G24" s="300" t="n"/>
+      <c r="H24" s="300" t="n"/>
+      <c r="I24" s="300" t="n"/>
+      <c r="J24" s="300" t="n"/>
+      <c r="K24" s="300" t="n"/>
+      <c r="L24" s="301" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" s="66">
+      <c r="B25" s="380" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="230" t="inlineStr">
+      <c r="C25" s="300" t="n"/>
+      <c r="D25" s="300" t="n"/>
+      <c r="E25" s="300" t="n"/>
+      <c r="F25" s="300" t="n"/>
+      <c r="G25" s="300" t="n"/>
+      <c r="H25" s="300" t="n"/>
+      <c r="I25" s="300" t="n"/>
+      <c r="J25" s="300" t="n"/>
+      <c r="K25" s="300" t="n"/>
+      <c r="L25" s="301" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" s="66">
+      <c r="B26" s="381" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="300" t="n"/>
+      <c r="D26" s="300" t="n"/>
+      <c r="E26" s="300" t="n"/>
+      <c r="F26" s="300" t="n"/>
+      <c r="G26" s="300" t="n"/>
+      <c r="H26" s="300" t="n"/>
+      <c r="I26" s="300" t="n"/>
+      <c r="J26" s="300" t="n"/>
+      <c r="K26" s="300" t="n"/>
+      <c r="L26" s="301" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" s="66">
+      <c r="B27" s="359" t="n"/>
+      <c r="C27" s="310" t="n"/>
+      <c r="D27" s="310" t="n"/>
+      <c r="E27" s="310" t="n"/>
+      <c r="F27" s="310" t="n"/>
+      <c r="G27" s="310" t="n"/>
+      <c r="H27" s="310" t="n"/>
+      <c r="I27" s="310" t="n"/>
+      <c r="J27" s="310" t="n"/>
+      <c r="K27" s="310" t="n"/>
+      <c r="L27" s="311" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -29942,7 +30840,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
       <c r="A3" s="237" t="inlineStr">
         <is>
@@ -30437,7 +31334,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
       <c r="A3" s="240" t="inlineStr">
         <is>
@@ -31184,7 +32080,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
       <c r="A3" s="245" t="inlineStr">
         <is>
@@ -31862,7 +32757,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
       <c r="A3" s="249" t="inlineStr">
         <is>
@@ -32412,7 +33306,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="66">
       <c r="A3" s="252" t="inlineStr">
         <is>
